--- a/pib_ec.xlsx
+++ b/pib_ec.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victormoralesonate/Documents/Consultorias&amp;Cursos/DataLectures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victormorales/Documents/Consultorias&amp;Cursos/DataLectures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{368910C6-EDE1-7946-B6D3-56B7171C5C2D}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12FC911-4DB4-3D4B-9949-E97EC740B803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15640" xr2:uid="{95E36FD9-C617-FF4F-9408-F48E435C498B}"/>
+    <workbookView xWindow="3800" yWindow="940" windowWidth="27640" windowHeight="15640" xr2:uid="{95E36FD9-C617-FF4F-9408-F48E435C498B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="milesUSD" sheetId="1" r:id="rId1"/>
+    <sheet name="USD2007" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">milesUSD!$A$1:$B$49</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="95">
   <si>
     <t>2000.I</t>
   </si>
@@ -249,25 +250,83 @@
     <t>PIB</t>
   </si>
   <si>
-    <t>Time</t>
+    <t>FBKF</t>
+  </si>
+  <si>
+    <t>Trimestres</t>
+  </si>
+  <si>
+    <t>2018.I</t>
+  </si>
+  <si>
+    <t>2018.II</t>
+  </si>
+  <si>
+    <t>2018.III</t>
+  </si>
+  <si>
+    <t>2018.IV</t>
+  </si>
+  <si>
+    <t>2019.I</t>
+  </si>
+  <si>
+    <t>2019.II</t>
+  </si>
+  <si>
+    <t>2019.III</t>
+  </si>
+  <si>
+    <t>2019.IV</t>
+  </si>
+  <si>
+    <t>2020.I</t>
+  </si>
+  <si>
+    <t>2020.II</t>
+  </si>
+  <si>
+    <t>2020.III</t>
+  </si>
+  <si>
+    <t>2020.IV</t>
+  </si>
+  <si>
+    <t>IMPOR</t>
+  </si>
+  <si>
+    <t>OF</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>GCFH</t>
+  </si>
+  <si>
+    <t>GCFGC</t>
+  </si>
+  <si>
+    <t>VE</t>
+  </si>
+  <si>
+    <t>EXPOR</t>
+  </si>
+  <si>
+    <t>UF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -606,591 +665,5967 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6A26F6-5C04-004E-9C6E-4D8E5C28C079}">
-  <dimension ref="A1:B73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:K85"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>9134587</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>3819126</v>
+      </c>
+      <c r="C2">
+        <v>1120302</v>
+      </c>
+      <c r="D2">
+        <v>4939428</v>
+      </c>
+      <c r="E2">
+        <v>3433046</v>
+      </c>
+      <c r="F2">
+        <v>2445053</v>
+      </c>
+      <c r="G2">
+        <v>175154</v>
+      </c>
+      <c r="H2">
+        <v>723232</v>
+      </c>
+      <c r="I2">
+        <v>89607</v>
+      </c>
+      <c r="J2">
+        <v>1506382</v>
+      </c>
+      <c r="K2">
+        <v>4939428</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>9320414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>4402479</v>
+      </c>
+      <c r="C3">
+        <v>1165977</v>
+      </c>
+      <c r="D3">
+        <v>5568456</v>
+      </c>
+      <c r="E3">
+        <v>4093878</v>
+      </c>
+      <c r="F3">
+        <v>2841942</v>
+      </c>
+      <c r="G3">
+        <v>389776</v>
+      </c>
+      <c r="H3">
+        <v>821301</v>
+      </c>
+      <c r="I3">
+        <v>40859</v>
+      </c>
+      <c r="J3">
+        <v>1474578</v>
+      </c>
+      <c r="K3">
+        <v>5568456</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>9548491</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>4906653</v>
+      </c>
+      <c r="C4">
+        <v>1344968</v>
+      </c>
+      <c r="D4">
+        <v>6251621</v>
+      </c>
+      <c r="E4">
+        <v>4758217</v>
+      </c>
+      <c r="F4">
+        <v>3164392</v>
+      </c>
+      <c r="G4">
+        <v>516011</v>
+      </c>
+      <c r="H4">
+        <v>947040</v>
+      </c>
+      <c r="I4">
+        <v>130774</v>
+      </c>
+      <c r="J4">
+        <v>1493404</v>
+      </c>
+      <c r="K4">
+        <v>6251621</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>9722918</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>5190343</v>
+      </c>
+      <c r="C5">
+        <v>1376539</v>
+      </c>
+      <c r="D5">
+        <v>6566882</v>
+      </c>
+      <c r="E5">
+        <v>5155931</v>
+      </c>
+      <c r="F5">
+        <v>3378859</v>
+      </c>
+      <c r="G5">
+        <v>631921</v>
+      </c>
+      <c r="H5">
+        <v>991669</v>
+      </c>
+      <c r="I5">
+        <v>153482</v>
+      </c>
+      <c r="J5">
+        <v>1410951</v>
+      </c>
+      <c r="K5">
+        <v>6566882</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>9699363</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>5904082</v>
+      </c>
+      <c r="C6">
+        <v>1558735</v>
+      </c>
+      <c r="D6">
+        <v>7462817</v>
+      </c>
+      <c r="E6">
+        <v>5965283</v>
+      </c>
+      <c r="F6">
+        <v>4198533</v>
+      </c>
+      <c r="G6">
+        <v>577101</v>
+      </c>
+      <c r="H6">
+        <v>1053487</v>
+      </c>
+      <c r="I6">
+        <v>136162</v>
+      </c>
+      <c r="J6">
+        <v>1497534</v>
+      </c>
+      <c r="K6">
+        <v>7462817</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>9802413</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>6069620</v>
+      </c>
+      <c r="C7">
+        <v>1656183</v>
+      </c>
+      <c r="D7">
+        <v>7725803</v>
+      </c>
+      <c r="E7">
+        <v>6337242</v>
+      </c>
+      <c r="F7">
+        <v>4375885</v>
+      </c>
+      <c r="G7">
+        <v>582004</v>
+      </c>
+      <c r="H7">
+        <v>1147563</v>
+      </c>
+      <c r="I7">
+        <v>231790</v>
+      </c>
+      <c r="J7">
+        <v>1388561</v>
+      </c>
+      <c r="K7">
+        <v>7725803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>9809483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>6159609</v>
+      </c>
+      <c r="C8">
+        <v>1693120</v>
+      </c>
+      <c r="D8">
+        <v>7852729</v>
+      </c>
+      <c r="E8">
+        <v>6445033</v>
+      </c>
+      <c r="F8">
+        <v>4454342</v>
+      </c>
+      <c r="G8">
+        <v>551198</v>
+      </c>
+      <c r="H8">
+        <v>1212577</v>
+      </c>
+      <c r="I8">
+        <v>226916</v>
+      </c>
+      <c r="J8">
+        <v>1407696</v>
+      </c>
+      <c r="K8">
+        <v>7852729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>9930104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>6335013</v>
+      </c>
+      <c r="C9">
+        <v>1826210</v>
+      </c>
+      <c r="D9">
+        <v>8161223</v>
+      </c>
+      <c r="E9">
+        <v>6772797</v>
+      </c>
+      <c r="F9">
+        <v>4711126</v>
+      </c>
+      <c r="G9">
+        <v>601693</v>
+      </c>
+      <c r="H9">
+        <v>1247952</v>
+      </c>
+      <c r="I9">
+        <v>212026</v>
+      </c>
+      <c r="J9">
+        <v>1388426</v>
+      </c>
+      <c r="K9">
+        <v>8161223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>10063566</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>6737551</v>
+      </c>
+      <c r="C10">
+        <v>1840720</v>
+      </c>
+      <c r="D10">
+        <v>8578271</v>
+      </c>
+      <c r="E10">
+        <v>7158409</v>
+      </c>
+      <c r="F10">
+        <v>4935609</v>
+      </c>
+      <c r="G10">
+        <v>622826</v>
+      </c>
+      <c r="H10">
+        <v>1388559</v>
+      </c>
+      <c r="I10">
+        <v>211415</v>
+      </c>
+      <c r="J10">
+        <v>1419862</v>
+      </c>
+      <c r="K10">
+        <v>8578271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>10205818</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>7086627</v>
+      </c>
+      <c r="C11">
+        <v>2073234</v>
+      </c>
+      <c r="D11">
+        <v>9159861</v>
+      </c>
+      <c r="E11">
+        <v>7644751</v>
+      </c>
+      <c r="F11">
+        <v>5165450</v>
+      </c>
+      <c r="G11">
+        <v>689584</v>
+      </c>
+      <c r="H11">
+        <v>1460080</v>
+      </c>
+      <c r="I11">
+        <v>329637</v>
+      </c>
+      <c r="J11">
+        <v>1515110</v>
+      </c>
+      <c r="K11">
+        <v>9159861</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>10274208</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>7294132</v>
+      </c>
+      <c r="C12">
+        <v>2054515</v>
+      </c>
+      <c r="D12">
+        <v>9348647</v>
+      </c>
+      <c r="E12">
+        <v>7776383</v>
+      </c>
+      <c r="F12">
+        <v>5297262</v>
+      </c>
+      <c r="G12">
+        <v>721936</v>
+      </c>
+      <c r="H12">
+        <v>1514534</v>
+      </c>
+      <c r="I12">
+        <v>242651</v>
+      </c>
+      <c r="J12">
+        <v>1572264</v>
+      </c>
+      <c r="K12">
+        <v>9348647</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>10305402</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>7430635</v>
+      </c>
+      <c r="C13">
+        <v>1992169</v>
+      </c>
+      <c r="D13">
+        <v>9422804</v>
+      </c>
+      <c r="E13">
+        <v>7794194</v>
+      </c>
+      <c r="F13">
+        <v>5401579</v>
+      </c>
+      <c r="G13">
+        <v>772712</v>
+      </c>
+      <c r="H13">
+        <v>1543432</v>
+      </c>
+      <c r="I13">
+        <v>76471</v>
+      </c>
+      <c r="J13">
+        <v>1628610</v>
+      </c>
+      <c r="K13">
+        <v>9422804</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>10440088</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>8011429</v>
+      </c>
+      <c r="C14">
+        <v>1981196</v>
+      </c>
+      <c r="D14">
+        <v>9992625</v>
+      </c>
+      <c r="E14">
+        <v>8202783</v>
+      </c>
+      <c r="F14">
+        <v>5667569</v>
+      </c>
+      <c r="G14">
+        <v>801090</v>
+      </c>
+      <c r="H14">
+        <v>1603484</v>
+      </c>
+      <c r="I14">
+        <v>130640</v>
+      </c>
+      <c r="J14">
+        <v>1789842</v>
+      </c>
+      <c r="K14">
+        <v>9992625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>10240791</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>7965078</v>
+      </c>
+      <c r="C15">
+        <v>1938272</v>
+      </c>
+      <c r="D15">
+        <v>9903350</v>
+      </c>
+      <c r="E15">
+        <v>8170004</v>
+      </c>
+      <c r="F15">
+        <v>5830682</v>
+      </c>
+      <c r="G15">
+        <v>870265</v>
+      </c>
+      <c r="H15">
+        <v>1552829</v>
+      </c>
+      <c r="I15">
+        <v>-83772</v>
+      </c>
+      <c r="J15">
+        <v>1733346</v>
+      </c>
+      <c r="K15">
+        <v>9903350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>10464381</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>8120465</v>
+      </c>
+      <c r="C16">
+        <v>1992243</v>
+      </c>
+      <c r="D16">
+        <v>10112708</v>
+      </c>
+      <c r="E16">
+        <v>8246184</v>
+      </c>
+      <c r="F16">
+        <v>5866442</v>
+      </c>
+      <c r="G16">
+        <v>889497</v>
+      </c>
+      <c r="H16">
+        <v>1529914</v>
+      </c>
+      <c r="I16">
+        <v>-39669</v>
+      </c>
+      <c r="J16">
+        <v>1866524</v>
+      </c>
+      <c r="K16">
+        <v>10112708</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>10816002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>8335886</v>
+      </c>
+      <c r="C17">
+        <v>2080793</v>
+      </c>
+      <c r="D17">
+        <v>10416679</v>
+      </c>
+      <c r="E17">
+        <v>8477084</v>
+      </c>
+      <c r="F17">
+        <v>5903082</v>
+      </c>
+      <c r="G17">
+        <v>913976</v>
+      </c>
+      <c r="H17">
+        <v>1554456</v>
+      </c>
+      <c r="I17">
+        <v>105570</v>
+      </c>
+      <c r="J17">
+        <v>1939595</v>
+      </c>
+      <c r="K17">
+        <v>10416679</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>11091411</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>8849273</v>
+      </c>
+      <c r="C18">
+        <v>2179849</v>
+      </c>
+      <c r="D18">
+        <v>11029122</v>
+      </c>
+      <c r="E18">
+        <v>9036018</v>
+      </c>
+      <c r="F18">
+        <v>6306606</v>
+      </c>
+      <c r="G18">
+        <v>989429</v>
+      </c>
+      <c r="H18">
+        <v>1651726</v>
+      </c>
+      <c r="I18">
+        <v>88257</v>
+      </c>
+      <c r="J18">
+        <v>1993104</v>
+      </c>
+      <c r="K18">
+        <v>11029122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19">
-        <v>11282549</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>9041596</v>
+      </c>
+      <c r="C19">
+        <v>2396630</v>
+      </c>
+      <c r="D19">
+        <v>11438226</v>
+      </c>
+      <c r="E19">
+        <v>9214496</v>
+      </c>
+      <c r="F19">
+        <v>6406699</v>
+      </c>
+      <c r="G19">
+        <v>1001661</v>
+      </c>
+      <c r="H19">
+        <v>1772561</v>
+      </c>
+      <c r="I19">
+        <v>33575</v>
+      </c>
+      <c r="J19">
+        <v>2223730</v>
+      </c>
+      <c r="K19">
+        <v>11438226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20">
-        <v>11403289</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>9207469</v>
+      </c>
+      <c r="C20">
+        <v>2406415</v>
+      </c>
+      <c r="D20">
+        <v>11613884</v>
+      </c>
+      <c r="E20">
+        <v>9293733</v>
+      </c>
+      <c r="F20">
+        <v>6405966</v>
+      </c>
+      <c r="G20">
+        <v>984387</v>
+      </c>
+      <c r="H20">
+        <v>1836724</v>
+      </c>
+      <c r="I20">
+        <v>66656</v>
+      </c>
+      <c r="J20">
+        <v>2320151</v>
+      </c>
+      <c r="K20">
+        <v>11613884</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>11629461</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>9493323</v>
+      </c>
+      <c r="C21">
+        <v>2571515</v>
+      </c>
+      <c r="D21">
+        <v>12064838</v>
+      </c>
+      <c r="E21">
+        <v>9616979</v>
+      </c>
+      <c r="F21">
+        <v>6668037</v>
+      </c>
+      <c r="G21">
+        <v>1007289</v>
+      </c>
+      <c r="H21">
+        <v>1948114</v>
+      </c>
+      <c r="I21">
+        <v>-6461</v>
+      </c>
+      <c r="J21">
+        <v>2447859</v>
+      </c>
+      <c r="K21">
+        <v>12064838</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22">
-        <v>11771814</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>9858210</v>
+      </c>
+      <c r="C22">
+        <v>2831624</v>
+      </c>
+      <c r="D22">
+        <v>12689834</v>
+      </c>
+      <c r="E22">
+        <v>10071654</v>
+      </c>
+      <c r="F22">
+        <v>6872973</v>
+      </c>
+      <c r="G22">
+        <v>1067573</v>
+      </c>
+      <c r="H22">
+        <v>1970809</v>
+      </c>
+      <c r="I22">
+        <v>160299</v>
+      </c>
+      <c r="J22">
+        <v>2618180</v>
+      </c>
+      <c r="K22">
+        <v>12689834</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23">
-        <v>11936392</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>10221018</v>
+      </c>
+      <c r="C23">
+        <v>2917386</v>
+      </c>
+      <c r="D23">
+        <v>13138404</v>
+      </c>
+      <c r="E23">
+        <v>10398551</v>
+      </c>
+      <c r="F23">
+        <v>7047351</v>
+      </c>
+      <c r="G23">
+        <v>1094043</v>
+      </c>
+      <c r="H23">
+        <v>2115210</v>
+      </c>
+      <c r="I23">
+        <v>141947</v>
+      </c>
+      <c r="J23">
+        <v>2739853</v>
+      </c>
+      <c r="K23">
+        <v>13138404</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24">
-        <v>11951919</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>10645973</v>
+      </c>
+      <c r="C24">
+        <v>2819573</v>
+      </c>
+      <c r="D24">
+        <v>13465546</v>
+      </c>
+      <c r="E24">
+        <v>10469920</v>
+      </c>
+      <c r="F24">
+        <v>7124759</v>
+      </c>
+      <c r="G24">
+        <v>1125814</v>
+      </c>
+      <c r="H24">
+        <v>2163922</v>
+      </c>
+      <c r="I24">
+        <v>55425</v>
+      </c>
+      <c r="J24">
+        <v>2995626</v>
+      </c>
+      <c r="K24">
+        <v>13465546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25">
-        <v>12149194</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>10781884</v>
+      </c>
+      <c r="C25">
+        <v>3253322</v>
+      </c>
+      <c r="D25">
+        <v>14035206</v>
+      </c>
+      <c r="E25">
+        <v>10925366</v>
+      </c>
+      <c r="F25">
+        <v>7390813</v>
+      </c>
+      <c r="G25">
+        <v>1161235</v>
+      </c>
+      <c r="H25">
+        <v>2226812</v>
+      </c>
+      <c r="I25">
+        <v>146506</v>
+      </c>
+      <c r="J25">
+        <v>3109840</v>
+      </c>
+      <c r="K25">
+        <v>14035206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26">
-        <v>12278116</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>11312589</v>
+      </c>
+      <c r="C26">
+        <v>3266788</v>
+      </c>
+      <c r="D26">
+        <v>14579377</v>
+      </c>
+      <c r="E26">
+        <v>11106132</v>
+      </c>
+      <c r="F26">
+        <v>7473628</v>
+      </c>
+      <c r="G26">
+        <v>1180967</v>
+      </c>
+      <c r="H26">
+        <v>2289331</v>
+      </c>
+      <c r="I26">
+        <v>162206</v>
+      </c>
+      <c r="J26">
+        <v>3473245</v>
+      </c>
+      <c r="K26">
+        <v>14579377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27">
-        <v>12447026</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>11727184</v>
+      </c>
+      <c r="C27">
+        <v>3419011</v>
+      </c>
+      <c r="D27">
+        <v>15146195</v>
+      </c>
+      <c r="E27">
+        <v>11629072</v>
+      </c>
+      <c r="F27">
+        <v>7640025</v>
+      </c>
+      <c r="G27">
+        <v>1213810</v>
+      </c>
+      <c r="H27">
+        <v>2446002</v>
+      </c>
+      <c r="I27">
+        <v>329235</v>
+      </c>
+      <c r="J27">
+        <v>3517123</v>
+      </c>
+      <c r="K27">
+        <v>15146195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28">
-        <v>12592998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>11941733</v>
+      </c>
+      <c r="C28">
+        <v>3529083</v>
+      </c>
+      <c r="D28">
+        <v>15470816</v>
+      </c>
+      <c r="E28">
+        <v>11923431</v>
+      </c>
+      <c r="F28">
+        <v>7792795</v>
+      </c>
+      <c r="G28">
+        <v>1244480</v>
+      </c>
+      <c r="H28">
+        <v>2546226</v>
+      </c>
+      <c r="I28">
+        <v>339930</v>
+      </c>
+      <c r="J28">
+        <v>3547385</v>
+      </c>
+      <c r="K28">
+        <v>15470816</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29">
-        <v>12596475</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>11820538</v>
+      </c>
+      <c r="C29">
+        <v>3534018</v>
+      </c>
+      <c r="D29">
+        <v>15354556</v>
+      </c>
+      <c r="E29">
+        <v>11695810</v>
+      </c>
+      <c r="F29">
+        <v>7974442</v>
+      </c>
+      <c r="G29">
+        <v>1322646</v>
+      </c>
+      <c r="H29">
+        <v>2478153</v>
+      </c>
+      <c r="I29">
+        <v>-79431</v>
+      </c>
+      <c r="J29">
+        <v>3658746</v>
+      </c>
+      <c r="K29">
+        <v>15354556</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30">
-        <v>12548685</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>11972101</v>
+      </c>
+      <c r="C30">
+        <v>3688804</v>
+      </c>
+      <c r="D30">
+        <v>15660905</v>
+      </c>
+      <c r="E30">
+        <v>12092597</v>
+      </c>
+      <c r="F30">
+        <v>8096780</v>
+      </c>
+      <c r="G30">
+        <v>1349454</v>
+      </c>
+      <c r="H30">
+        <v>2580234</v>
+      </c>
+      <c r="I30">
+        <v>66129</v>
+      </c>
+      <c r="J30">
+        <v>3568308</v>
+      </c>
+      <c r="K30">
+        <v>15660905</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31">
-        <v>12641374</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>12483035</v>
+      </c>
+      <c r="C31">
+        <v>3756612</v>
+      </c>
+      <c r="D31">
+        <v>16239647</v>
+      </c>
+      <c r="E31">
+        <v>12380699</v>
+      </c>
+      <c r="F31">
+        <v>8215569</v>
+      </c>
+      <c r="G31">
+        <v>1402301</v>
+      </c>
+      <c r="H31">
+        <v>2613022</v>
+      </c>
+      <c r="I31">
+        <v>149807</v>
+      </c>
+      <c r="J31">
+        <v>3858948</v>
+      </c>
+      <c r="K31">
+        <v>16239647</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32">
-        <v>12821498</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>12923037</v>
+      </c>
+      <c r="C32">
+        <v>3839378</v>
+      </c>
+      <c r="D32">
+        <v>16762415</v>
+      </c>
+      <c r="E32">
+        <v>12641456</v>
+      </c>
+      <c r="F32">
+        <v>8348009</v>
+      </c>
+      <c r="G32">
+        <v>1407775</v>
+      </c>
+      <c r="H32">
+        <v>2631842</v>
+      </c>
+      <c r="I32">
+        <v>253830</v>
+      </c>
+      <c r="J32">
+        <v>4120959</v>
+      </c>
+      <c r="K32">
+        <v>16762415</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>31</v>
       </c>
       <c r="B33">
-        <v>12996220</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>13629604</v>
+      </c>
+      <c r="C33">
+        <v>4351829</v>
+      </c>
+      <c r="D33">
+        <v>17981433</v>
+      </c>
+      <c r="E33">
+        <v>13241963</v>
+      </c>
+      <c r="F33">
+        <v>8540920</v>
+      </c>
+      <c r="G33">
+        <v>1414679</v>
+      </c>
+      <c r="H33">
+        <v>2768849</v>
+      </c>
+      <c r="I33">
+        <v>517515</v>
+      </c>
+      <c r="J33">
+        <v>4739470</v>
+      </c>
+      <c r="K33">
+        <v>17981433</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
       <c r="B34">
-        <v>13203590</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>14505871</v>
+      </c>
+      <c r="C34">
+        <v>4858594</v>
+      </c>
+      <c r="D34">
+        <v>19364465</v>
+      </c>
+      <c r="E34">
+        <v>13704003</v>
+      </c>
+      <c r="F34">
+        <v>8948763</v>
+      </c>
+      <c r="G34">
+        <v>1670986</v>
+      </c>
+      <c r="H34">
+        <v>2970329</v>
+      </c>
+      <c r="I34">
+        <v>113925</v>
+      </c>
+      <c r="J34">
+        <v>5660462</v>
+      </c>
+      <c r="K34">
+        <v>19364465</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="B35">
-        <v>13437956</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>15788923</v>
+      </c>
+      <c r="C35">
+        <v>5288903</v>
+      </c>
+      <c r="D35">
+        <v>21077826</v>
+      </c>
+      <c r="E35">
+        <v>15492213</v>
+      </c>
+      <c r="F35">
+        <v>9312999</v>
+      </c>
+      <c r="G35">
+        <v>1800173</v>
+      </c>
+      <c r="H35">
+        <v>3344536</v>
+      </c>
+      <c r="I35">
+        <v>1034505</v>
+      </c>
+      <c r="J35">
+        <v>5585613</v>
+      </c>
+      <c r="K35">
+        <v>21077826</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>34</v>
       </c>
       <c r="B36">
-        <v>13689235</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>16213465</v>
+      </c>
+      <c r="C36">
+        <v>5621373</v>
+      </c>
+      <c r="D36">
+        <v>21834838</v>
+      </c>
+      <c r="E36">
+        <v>16529274</v>
+      </c>
+      <c r="F36">
+        <v>9664597</v>
+      </c>
+      <c r="G36">
+        <v>1902052</v>
+      </c>
+      <c r="H36">
+        <v>3703868</v>
+      </c>
+      <c r="I36">
+        <v>1258757</v>
+      </c>
+      <c r="J36">
+        <v>5305564</v>
+      </c>
+      <c r="K36">
+        <v>21834838</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37">
-        <v>13919627</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>15254376</v>
+      </c>
+      <c r="C37">
+        <v>5164530</v>
+      </c>
+      <c r="D37">
+        <v>20418906</v>
+      </c>
+      <c r="E37">
+        <v>15870181</v>
+      </c>
+      <c r="F37">
+        <v>10064904</v>
+      </c>
+      <c r="G37">
+        <v>1933577</v>
+      </c>
+      <c r="H37">
+        <v>3799781</v>
+      </c>
+      <c r="I37">
+        <v>71919</v>
+      </c>
+      <c r="J37">
+        <v>4548725</v>
+      </c>
+      <c r="K37">
+        <v>20418906</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>36</v>
       </c>
       <c r="B38">
-        <v>13721197</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>15022003</v>
+      </c>
+      <c r="C38">
+        <v>4293031</v>
+      </c>
+      <c r="D38">
+        <v>19315034</v>
+      </c>
+      <c r="E38">
+        <v>15585684</v>
+      </c>
+      <c r="F38">
+        <v>9799156</v>
+      </c>
+      <c r="G38">
+        <v>2020721</v>
+      </c>
+      <c r="H38">
+        <v>3638386</v>
+      </c>
+      <c r="I38">
+        <v>127421</v>
+      </c>
+      <c r="J38">
+        <v>3729350</v>
+      </c>
+      <c r="K38">
+        <v>19315034</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>37</v>
       </c>
       <c r="B39">
-        <v>13663730</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>15588869</v>
+      </c>
+      <c r="C39">
+        <v>4024805</v>
+      </c>
+      <c r="D39">
+        <v>19613674</v>
+      </c>
+      <c r="E39">
+        <v>15813110</v>
+      </c>
+      <c r="F39">
+        <v>9634405</v>
+      </c>
+      <c r="G39">
+        <v>2100079</v>
+      </c>
+      <c r="H39">
+        <v>3538406</v>
+      </c>
+      <c r="I39">
+        <v>540220</v>
+      </c>
+      <c r="J39">
+        <v>3800564</v>
+      </c>
+      <c r="K39">
+        <v>19613674</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>38</v>
       </c>
       <c r="B40">
-        <v>13579505</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>15779977</v>
+      </c>
+      <c r="C40">
+        <v>4134711</v>
+      </c>
+      <c r="D40">
+        <v>19914688</v>
+      </c>
+      <c r="E40">
+        <v>15992901</v>
+      </c>
+      <c r="F40">
+        <v>9658411</v>
+      </c>
+      <c r="G40">
+        <v>2189216</v>
+      </c>
+      <c r="H40">
+        <v>3493945</v>
+      </c>
+      <c r="I40">
+        <v>651329</v>
+      </c>
+      <c r="J40">
+        <v>3921787</v>
+      </c>
+      <c r="K40">
+        <v>19914688</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>39</v>
       </c>
       <c r="B41">
-        <v>13593300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>16128837</v>
+      </c>
+      <c r="C41">
+        <v>4337578</v>
+      </c>
+      <c r="D41">
+        <v>20466415</v>
+      </c>
+      <c r="E41">
+        <v>16132453</v>
+      </c>
+      <c r="F41">
+        <v>9821313</v>
+      </c>
+      <c r="G41">
+        <v>2271259</v>
+      </c>
+      <c r="H41">
+        <v>3586952</v>
+      </c>
+      <c r="I41">
+        <v>452929</v>
+      </c>
+      <c r="J41">
+        <v>4333962</v>
+      </c>
+      <c r="K41">
+        <v>20466415</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>40</v>
       </c>
       <c r="B42">
-        <v>13729815</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>16762628</v>
+      </c>
+      <c r="C42">
+        <v>5116967</v>
+      </c>
+      <c r="D42">
+        <v>21879595</v>
+      </c>
+      <c r="E42">
+        <v>17393969</v>
+      </c>
+      <c r="F42">
+        <v>10500363</v>
+      </c>
+      <c r="G42">
+        <v>2234239</v>
+      </c>
+      <c r="H42">
+        <v>3975994</v>
+      </c>
+      <c r="I42">
+        <v>683373</v>
+      </c>
+      <c r="J42">
+        <v>4485626</v>
+      </c>
+      <c r="K42">
+        <v>21879595</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>41</v>
       </c>
       <c r="B43">
-        <v>13946256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>17070795</v>
+      </c>
+      <c r="C43">
+        <v>5465911</v>
+      </c>
+      <c r="D43">
+        <v>22536706</v>
+      </c>
+      <c r="E43">
+        <v>17718822</v>
+      </c>
+      <c r="F43">
+        <v>10805848</v>
+      </c>
+      <c r="G43">
+        <v>2241678</v>
+      </c>
+      <c r="H43">
+        <v>4168368</v>
+      </c>
+      <c r="I43">
+        <v>502928</v>
+      </c>
+      <c r="J43">
+        <v>4817884</v>
+      </c>
+      <c r="K43">
+        <v>22536706</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>42</v>
       </c>
       <c r="B44">
-        <v>14175891</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>17429358</v>
+      </c>
+      <c r="C44">
+        <v>5914138</v>
+      </c>
+      <c r="D44">
+        <v>23343496</v>
+      </c>
+      <c r="E44">
+        <v>18583801</v>
+      </c>
+      <c r="F44">
+        <v>11235105</v>
+      </c>
+      <c r="G44">
+        <v>2301804</v>
+      </c>
+      <c r="H44">
+        <v>4422541</v>
+      </c>
+      <c r="I44">
+        <v>624351</v>
+      </c>
+      <c r="J44">
+        <v>4759695</v>
+      </c>
+      <c r="K44">
+        <v>23343496</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>43</v>
       </c>
       <c r="B45">
-        <v>14629093</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>18292586</v>
+      </c>
+      <c r="C45">
+        <v>6044684</v>
+      </c>
+      <c r="D45">
+        <v>24337270</v>
+      </c>
+      <c r="E45">
+        <v>18998036</v>
+      </c>
+      <c r="F45">
+        <v>11470789</v>
+      </c>
+      <c r="G45">
+        <v>2403346</v>
+      </c>
+      <c r="H45">
+        <v>4560986</v>
+      </c>
+      <c r="I45">
+        <v>562915</v>
+      </c>
+      <c r="J45">
+        <v>5339234</v>
+      </c>
+      <c r="K45">
+        <v>24337270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>44</v>
       </c>
       <c r="B46">
-        <v>14790364</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>18922955</v>
+      </c>
+      <c r="C46">
+        <v>6105619</v>
+      </c>
+      <c r="D46">
+        <v>25028574</v>
+      </c>
+      <c r="E46">
+        <v>19332633</v>
+      </c>
+      <c r="F46">
+        <v>11694784</v>
+      </c>
+      <c r="G46">
+        <v>2379105</v>
+      </c>
+      <c r="H46">
+        <v>4765661</v>
+      </c>
+      <c r="I46">
+        <v>493083</v>
+      </c>
+      <c r="J46">
+        <v>5695941</v>
+      </c>
+      <c r="K46">
+        <v>25028574</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>45</v>
       </c>
       <c r="B47">
-        <v>15176741</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>19728114</v>
+      </c>
+      <c r="C47">
+        <v>6576850</v>
+      </c>
+      <c r="D47">
+        <v>26304964</v>
+      </c>
+      <c r="E47">
+        <v>20202381</v>
+      </c>
+      <c r="F47">
+        <v>12040630</v>
+      </c>
+      <c r="G47">
+        <v>2539852</v>
+      </c>
+      <c r="H47">
+        <v>5002022</v>
+      </c>
+      <c r="I47">
+        <v>619877</v>
+      </c>
+      <c r="J47">
+        <v>6102583</v>
+      </c>
+      <c r="K47">
+        <v>26304964</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>46</v>
       </c>
       <c r="B48">
-        <v>15409103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>19968470</v>
+      </c>
+      <c r="C48">
+        <v>6692488</v>
+      </c>
+      <c r="D48">
+        <v>26660958</v>
+      </c>
+      <c r="E48">
+        <v>20258364</v>
+      </c>
+      <c r="F48">
+        <v>12359537</v>
+      </c>
+      <c r="G48">
+        <v>2534436</v>
+      </c>
+      <c r="H48">
+        <v>5222935</v>
+      </c>
+      <c r="I48">
+        <v>141456</v>
+      </c>
+      <c r="J48">
+        <v>6402594</v>
+      </c>
+      <c r="K48">
+        <v>26660958</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>47</v>
       </c>
       <c r="B49">
-        <v>15548856</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>20657125</v>
+      </c>
+      <c r="C49">
+        <v>7078904</v>
+      </c>
+      <c r="D49">
+        <v>27736029</v>
+      </c>
+      <c r="E49">
+        <v>21265298</v>
+      </c>
+      <c r="F49">
+        <v>12562204</v>
+      </c>
+      <c r="G49">
+        <v>2637773</v>
+      </c>
+      <c r="H49">
+        <v>5480168</v>
+      </c>
+      <c r="I49">
+        <v>585153</v>
+      </c>
+      <c r="J49">
+        <v>6470731</v>
+      </c>
+      <c r="K49">
+        <v>27736029</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>48</v>
       </c>
       <c r="B50">
-        <v>15798590</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>21622937</v>
+      </c>
+      <c r="C50">
+        <v>6853963</v>
+      </c>
+      <c r="D50">
+        <v>28476900</v>
+      </c>
+      <c r="E50">
+        <v>21791681</v>
+      </c>
+      <c r="F50">
+        <v>12896279</v>
+      </c>
+      <c r="G50">
+        <v>2805829</v>
+      </c>
+      <c r="H50">
+        <v>5733341</v>
+      </c>
+      <c r="I50">
+        <v>356232</v>
+      </c>
+      <c r="J50">
+        <v>6685219</v>
+      </c>
+      <c r="K50">
+        <v>28476900</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51">
-        <v>16072842</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>21908844</v>
+      </c>
+      <c r="C51">
+        <v>6883063</v>
+      </c>
+      <c r="D51">
+        <v>28791907</v>
+      </c>
+      <c r="E51">
+        <v>22192062</v>
+      </c>
+      <c r="F51">
+        <v>13257745</v>
+      </c>
+      <c r="G51">
+        <v>2847288</v>
+      </c>
+      <c r="H51">
+        <v>5853906</v>
+      </c>
+      <c r="I51">
+        <v>233123</v>
+      </c>
+      <c r="J51">
+        <v>6599845</v>
+      </c>
+      <c r="K51">
+        <v>28791907</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>50</v>
       </c>
       <c r="B52">
-        <v>16196959</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>22106937</v>
+      </c>
+      <c r="C52">
+        <v>7035012</v>
+      </c>
+      <c r="D52">
+        <v>29141949</v>
+      </c>
+      <c r="E52">
+        <v>22469556</v>
+      </c>
+      <c r="F52">
+        <v>13364281</v>
+      </c>
+      <c r="G52">
+        <v>2951086</v>
+      </c>
+      <c r="H52">
+        <v>5997916</v>
+      </c>
+      <c r="I52">
+        <v>156273</v>
+      </c>
+      <c r="J52">
+        <v>6672393</v>
+      </c>
+      <c r="K52">
+        <v>29141949</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>51</v>
       </c>
       <c r="B53">
-        <v>16294042</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>22285826</v>
+      </c>
+      <c r="C53">
+        <v>7000075</v>
+      </c>
+      <c r="D53">
+        <v>29285901</v>
+      </c>
+      <c r="E53">
+        <v>22721087</v>
+      </c>
+      <c r="F53">
+        <v>13489967</v>
+      </c>
+      <c r="G53">
+        <v>3122549</v>
+      </c>
+      <c r="H53">
+        <v>6122675</v>
+      </c>
+      <c r="I53">
+        <v>-14104</v>
+      </c>
+      <c r="J53">
+        <v>6564814</v>
+      </c>
+      <c r="K53">
+        <v>29285901</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>52</v>
       </c>
       <c r="B54">
-        <v>16458713</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>23019786</v>
+      </c>
+      <c r="C54">
+        <v>7287332</v>
+      </c>
+      <c r="D54">
+        <v>30307118</v>
+      </c>
+      <c r="E54">
+        <v>23717022</v>
+      </c>
+      <c r="F54">
+        <v>13748778</v>
+      </c>
+      <c r="G54">
+        <v>3222907</v>
+      </c>
+      <c r="H54">
+        <v>6406446</v>
+      </c>
+      <c r="I54">
+        <v>338891</v>
+      </c>
+      <c r="J54">
+        <v>6590096</v>
+      </c>
+      <c r="K54">
+        <v>30307118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>53</v>
       </c>
       <c r="B55">
-        <v>16802240</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>23441324</v>
+      </c>
+      <c r="C55">
+        <v>7370541</v>
+      </c>
+      <c r="D55">
+        <v>30811865</v>
+      </c>
+      <c r="E55">
+        <v>24184056</v>
+      </c>
+      <c r="F55">
+        <v>14137037</v>
+      </c>
+      <c r="G55">
+        <v>3311670</v>
+      </c>
+      <c r="H55">
+        <v>6509500</v>
+      </c>
+      <c r="I55">
+        <v>225849</v>
+      </c>
+      <c r="J55">
+        <v>6627809</v>
+      </c>
+      <c r="K55">
+        <v>30811865</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>54</v>
       </c>
       <c r="B56">
-        <v>17131619</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>24238576</v>
+      </c>
+      <c r="C56">
+        <v>7448982</v>
+      </c>
+      <c r="D56">
+        <v>31687558</v>
+      </c>
+      <c r="E56">
+        <v>24759564</v>
+      </c>
+      <c r="F56">
+        <v>14384933</v>
+      </c>
+      <c r="G56">
+        <v>3375221</v>
+      </c>
+      <c r="H56">
+        <v>6637009</v>
+      </c>
+      <c r="I56">
+        <v>362401</v>
+      </c>
+      <c r="J56">
+        <v>6927994</v>
+      </c>
+      <c r="K56">
+        <v>31687558</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>55</v>
       </c>
       <c r="B57">
-        <v>17153556</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>24429973</v>
+      </c>
+      <c r="C57">
+        <v>7352772</v>
+      </c>
+      <c r="D57">
+        <v>31782745</v>
+      </c>
+      <c r="E57">
+        <v>24685138</v>
+      </c>
+      <c r="F57">
+        <v>14671139</v>
+      </c>
+      <c r="G57">
+        <v>3413480</v>
+      </c>
+      <c r="H57">
+        <v>6658705</v>
+      </c>
+      <c r="I57">
+        <v>-58186</v>
+      </c>
+      <c r="J57">
+        <v>7097607</v>
+      </c>
+      <c r="K57">
+        <v>31782745</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>56</v>
       </c>
       <c r="B58">
-        <v>17096076</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>24829431</v>
+      </c>
+      <c r="C58">
+        <v>7213516</v>
+      </c>
+      <c r="D58">
+        <v>32042947</v>
+      </c>
+      <c r="E58">
+        <v>24566143</v>
+      </c>
+      <c r="F58">
+        <v>14517583</v>
+      </c>
+      <c r="G58">
+        <v>3405399</v>
+      </c>
+      <c r="H58">
+        <v>6612209</v>
+      </c>
+      <c r="I58">
+        <v>30952</v>
+      </c>
+      <c r="J58">
+        <v>7476804</v>
+      </c>
+      <c r="K58">
+        <v>32042947</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>57</v>
       </c>
       <c r="B59">
-        <v>17494063</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>25540887</v>
+      </c>
+      <c r="C59">
+        <v>7600587</v>
+      </c>
+      <c r="D59">
+        <v>33141474</v>
+      </c>
+      <c r="E59">
+        <v>25817961</v>
+      </c>
+      <c r="F59">
+        <v>14911182</v>
+      </c>
+      <c r="G59">
+        <v>3619811</v>
+      </c>
+      <c r="H59">
+        <v>6815031</v>
+      </c>
+      <c r="I59">
+        <v>471937</v>
+      </c>
+      <c r="J59">
+        <v>7323513</v>
+      </c>
+      <c r="K59">
+        <v>33141474</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>58</v>
       </c>
       <c r="B60">
-        <v>17736022</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>25940400</v>
+      </c>
+      <c r="C60">
+        <v>7757947</v>
+      </c>
+      <c r="D60">
+        <v>33698347</v>
+      </c>
+      <c r="E60">
+        <v>26652356</v>
+      </c>
+      <c r="F60">
+        <v>15235324</v>
+      </c>
+      <c r="G60">
+        <v>3692677</v>
+      </c>
+      <c r="H60">
+        <v>7107289</v>
+      </c>
+      <c r="I60">
+        <v>617066</v>
+      </c>
+      <c r="J60">
+        <v>7045991</v>
+      </c>
+      <c r="K60">
+        <v>33698347</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>59</v>
       </c>
       <c r="B61">
-        <v>17779201</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>25415613</v>
+      </c>
+      <c r="C61">
+        <v>7596231</v>
+      </c>
+      <c r="D61">
+        <v>33011844</v>
+      </c>
+      <c r="E61">
+        <v>26322030</v>
+      </c>
+      <c r="F61">
+        <v>15348207</v>
+      </c>
+      <c r="G61">
+        <v>3825068</v>
+      </c>
+      <c r="H61">
+        <v>7149702</v>
+      </c>
+      <c r="I61">
+        <v>-947</v>
+      </c>
+      <c r="J61">
+        <v>6689814</v>
+      </c>
+      <c r="K61">
+        <v>33011844</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>60</v>
       </c>
       <c r="B62">
-        <v>17816050</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>25052739</v>
+      </c>
+      <c r="C62">
+        <v>6741430</v>
+      </c>
+      <c r="D62">
+        <v>31794169</v>
+      </c>
+      <c r="E62">
+        <v>25959715</v>
+      </c>
+      <c r="F62">
+        <v>15462530</v>
+      </c>
+      <c r="G62">
+        <v>3615215</v>
+      </c>
+      <c r="H62">
+        <v>6782799</v>
+      </c>
+      <c r="I62">
+        <v>99171</v>
+      </c>
+      <c r="J62">
+        <v>5834454</v>
+      </c>
+      <c r="K62">
+        <v>31794169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>61</v>
       </c>
       <c r="B63">
-        <v>17537769</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>25086195</v>
+      </c>
+      <c r="C63">
+        <v>6236883</v>
+      </c>
+      <c r="D63">
+        <v>31323078</v>
+      </c>
+      <c r="E63">
+        <v>25949666</v>
+      </c>
+      <c r="F63">
+        <v>15298830</v>
+      </c>
+      <c r="G63">
+        <v>3611008</v>
+      </c>
+      <c r="H63">
+        <v>6611841</v>
+      </c>
+      <c r="I63">
+        <v>427987</v>
+      </c>
+      <c r="J63">
+        <v>5373412</v>
+      </c>
+      <c r="K63">
+        <v>31323078</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>62</v>
       </c>
       <c r="B64">
-        <v>17492225</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>24779738</v>
+      </c>
+      <c r="C64">
+        <v>5590112</v>
+      </c>
+      <c r="D64">
+        <v>30369850</v>
+      </c>
+      <c r="E64">
+        <v>25283275</v>
+      </c>
+      <c r="F64">
+        <v>15254879</v>
+      </c>
+      <c r="G64">
+        <v>3603087</v>
+      </c>
+      <c r="H64">
+        <v>6482288</v>
+      </c>
+      <c r="I64">
+        <v>-56979</v>
+      </c>
+      <c r="J64">
+        <v>5086575</v>
+      </c>
+      <c r="K64">
+        <v>30369850</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>63</v>
       </c>
       <c r="B65">
-        <v>17328633</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>24371709</v>
+      </c>
+      <c r="C65">
+        <v>5247024</v>
+      </c>
+      <c r="D65">
+        <v>29618733</v>
+      </c>
+      <c r="E65">
+        <v>24805805</v>
+      </c>
+      <c r="F65">
+        <v>14975671</v>
+      </c>
+      <c r="G65">
+        <v>3497818</v>
+      </c>
+      <c r="H65">
+        <v>6513528</v>
+      </c>
+      <c r="I65">
+        <v>-181212</v>
+      </c>
+      <c r="J65">
+        <v>4812928</v>
+      </c>
+      <c r="K65">
+        <v>29618733</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>64</v>
       </c>
       <c r="B66">
-        <v>17094720</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>24913573</v>
+      </c>
+      <c r="C66">
+        <v>4698403</v>
+      </c>
+      <c r="D66">
+        <v>29611976</v>
+      </c>
+      <c r="E66">
+        <v>25003659</v>
+      </c>
+      <c r="F66">
+        <v>15272408</v>
+      </c>
+      <c r="G66">
+        <v>3632411</v>
+      </c>
+      <c r="H66">
+        <v>6363450</v>
+      </c>
+      <c r="I66">
+        <v>-264610</v>
+      </c>
+      <c r="J66">
+        <v>4608317</v>
+      </c>
+      <c r="K66">
+        <v>29611976</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>65</v>
       </c>
       <c r="B67">
-        <v>17240451</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>24926186</v>
+      </c>
+      <c r="C67">
+        <v>4585837</v>
+      </c>
+      <c r="D67">
+        <v>29512023</v>
+      </c>
+      <c r="E67">
+        <v>24721688</v>
+      </c>
+      <c r="F67">
+        <v>14963699</v>
+      </c>
+      <c r="G67">
+        <v>3668803</v>
+      </c>
+      <c r="H67">
+        <v>6222531</v>
+      </c>
+      <c r="I67">
+        <v>-133345</v>
+      </c>
+      <c r="J67">
+        <v>4790335</v>
+      </c>
+      <c r="K67">
+        <v>29512023</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>66</v>
       </c>
       <c r="B68">
-        <v>17233968</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>24910741</v>
+      </c>
+      <c r="C68">
+        <v>4766834</v>
+      </c>
+      <c r="D68">
+        <v>29677575</v>
+      </c>
+      <c r="E68">
+        <v>24777006</v>
+      </c>
+      <c r="F68">
+        <v>14867587</v>
+      </c>
+      <c r="G68">
+        <v>3634828</v>
+      </c>
+      <c r="H68">
+        <v>6262810</v>
+      </c>
+      <c r="I68">
+        <v>11781</v>
+      </c>
+      <c r="J68">
+        <v>4900569</v>
+      </c>
+      <c r="K68">
+        <v>29677575</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>67</v>
       </c>
       <c r="B69">
-        <v>17499319</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>25187196</v>
+      </c>
+      <c r="C69">
+        <v>4953627</v>
+      </c>
+      <c r="D69">
+        <v>30140823</v>
+      </c>
+      <c r="E69">
+        <v>24947405</v>
+      </c>
+      <c r="F69">
+        <v>14785998</v>
+      </c>
+      <c r="G69">
+        <v>3660552</v>
+      </c>
+      <c r="H69">
+        <v>6231997</v>
+      </c>
+      <c r="I69">
+        <v>268858</v>
+      </c>
+      <c r="J69">
+        <v>5193418</v>
+      </c>
+      <c r="K69">
+        <v>30140823</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>68</v>
       </c>
       <c r="B70">
-        <v>17558804</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>26000261</v>
+      </c>
+      <c r="C70">
+        <v>5313744</v>
+      </c>
+      <c r="D70">
+        <v>31314005</v>
+      </c>
+      <c r="E70">
+        <v>25941445</v>
+      </c>
+      <c r="F70">
+        <v>15633202</v>
+      </c>
+      <c r="G70">
+        <v>3738191</v>
+      </c>
+      <c r="H70">
+        <v>6549822</v>
+      </c>
+      <c r="I70">
+        <v>20230</v>
+      </c>
+      <c r="J70">
+        <v>5372560</v>
+      </c>
+      <c r="K70">
+        <v>31314005</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>69</v>
       </c>
       <c r="B71">
-        <v>17757789</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>25993550</v>
+      </c>
+      <c r="C71">
+        <v>5481790</v>
+      </c>
+      <c r="D71">
+        <v>31475340</v>
+      </c>
+      <c r="E71">
+        <v>26224741</v>
+      </c>
+      <c r="F71">
+        <v>15645616</v>
+      </c>
+      <c r="G71">
+        <v>3773698</v>
+      </c>
+      <c r="H71">
+        <v>6592246</v>
+      </c>
+      <c r="I71">
+        <v>213181</v>
+      </c>
+      <c r="J71">
+        <v>5250599</v>
+      </c>
+      <c r="K71">
+        <v>31475340</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>70</v>
       </c>
       <c r="B72">
-        <v>17803378</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>25960907</v>
+      </c>
+      <c r="C72">
+        <v>5736237</v>
+      </c>
+      <c r="D72">
+        <v>31697144</v>
+      </c>
+      <c r="E72">
+        <v>26262464</v>
+      </c>
+      <c r="F72">
+        <v>15603095</v>
+      </c>
+      <c r="G72">
+        <v>3827485</v>
+      </c>
+      <c r="H72">
+        <v>6635603</v>
+      </c>
+      <c r="I72">
+        <v>196281</v>
+      </c>
+      <c r="J72">
+        <v>5434680</v>
+      </c>
+      <c r="K72">
+        <v>31697144</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>71</v>
       </c>
       <c r="B73">
-        <v>18019265</v>
+        <v>26341144</v>
+      </c>
+      <c r="C73">
+        <v>5984562</v>
+      </c>
+      <c r="D73">
+        <v>32325706</v>
+      </c>
+      <c r="E73">
+        <v>26655778</v>
+      </c>
+      <c r="F73">
+        <v>15596074</v>
+      </c>
+      <c r="G73">
+        <v>3857844</v>
+      </c>
+      <c r="H73">
+        <v>6718585</v>
+      </c>
+      <c r="I73">
+        <v>483275</v>
+      </c>
+      <c r="J73">
+        <v>5669928</v>
+      </c>
+      <c r="K73">
+        <v>32325706</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74">
+        <v>26510612</v>
+      </c>
+      <c r="C74">
+        <v>6166397</v>
+      </c>
+      <c r="D74">
+        <v>32677009</v>
+      </c>
+      <c r="E74">
+        <v>26438576</v>
+      </c>
+      <c r="F74">
+        <v>15690603</v>
+      </c>
+      <c r="G74">
+        <v>3856675</v>
+      </c>
+      <c r="H74">
+        <v>6900492</v>
+      </c>
+      <c r="I74">
+        <v>-9194</v>
+      </c>
+      <c r="J74">
+        <v>6238433</v>
+      </c>
+      <c r="K74">
+        <v>32677009</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75">
+        <v>26761827</v>
+      </c>
+      <c r="C75">
+        <v>6318441</v>
+      </c>
+      <c r="D75">
+        <v>33080268</v>
+      </c>
+      <c r="E75">
+        <v>26994028</v>
+      </c>
+      <c r="F75">
+        <v>15950509</v>
+      </c>
+      <c r="G75">
+        <v>3960438</v>
+      </c>
+      <c r="H75">
+        <v>6940983</v>
+      </c>
+      <c r="I75">
+        <v>142098</v>
+      </c>
+      <c r="J75">
+        <v>6086240</v>
+      </c>
+      <c r="K75">
+        <v>33080268</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76">
+        <v>27078404</v>
+      </c>
+      <c r="C76">
+        <v>6448573</v>
+      </c>
+      <c r="D76">
+        <v>33526977</v>
+      </c>
+      <c r="E76">
+        <v>27538492</v>
+      </c>
+      <c r="F76">
+        <v>16185856</v>
+      </c>
+      <c r="G76">
+        <v>3967589</v>
+      </c>
+      <c r="H76">
+        <v>6900122</v>
+      </c>
+      <c r="I76">
+        <v>484925</v>
+      </c>
+      <c r="J76">
+        <v>5988485</v>
+      </c>
+      <c r="K76">
+        <v>33526977</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77">
+        <v>27211165</v>
+      </c>
+      <c r="C77">
+        <v>6620576</v>
+      </c>
+      <c r="D77">
+        <v>33831741</v>
+      </c>
+      <c r="E77">
+        <v>27830847</v>
+      </c>
+      <c r="F77">
+        <v>16375332</v>
+      </c>
+      <c r="G77">
+        <v>4044508</v>
+      </c>
+      <c r="H77">
+        <v>6776087</v>
+      </c>
+      <c r="I77">
+        <v>634920</v>
+      </c>
+      <c r="J77">
+        <v>6000894</v>
+      </c>
+      <c r="K77">
+        <v>33831741</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78">
+        <v>26914897</v>
+      </c>
+      <c r="C78">
+        <v>6305291</v>
+      </c>
+      <c r="D78">
+        <v>33220188</v>
+      </c>
+      <c r="E78">
+        <v>27132433</v>
+      </c>
+      <c r="F78">
+        <v>16037161</v>
+      </c>
+      <c r="G78">
+        <v>3868308</v>
+      </c>
+      <c r="H78">
+        <v>6679266</v>
+      </c>
+      <c r="I78">
+        <v>547698</v>
+      </c>
+      <c r="J78">
+        <v>6087755</v>
+      </c>
+      <c r="K78">
+        <v>33220188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79">
+        <v>27058331</v>
+      </c>
+      <c r="C79">
+        <v>6457067</v>
+      </c>
+      <c r="D79">
+        <v>33515398</v>
+      </c>
+      <c r="E79">
+        <v>27088904</v>
+      </c>
+      <c r="F79">
+        <v>16123571</v>
+      </c>
+      <c r="G79">
+        <v>3873160</v>
+      </c>
+      <c r="H79">
+        <v>6781244</v>
+      </c>
+      <c r="I79">
+        <v>310929</v>
+      </c>
+      <c r="J79">
+        <v>6426494</v>
+      </c>
+      <c r="K79">
+        <v>33515398</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80">
+        <v>27054758</v>
+      </c>
+      <c r="C80">
+        <v>6212133</v>
+      </c>
+      <c r="D80">
+        <v>33266891</v>
+      </c>
+      <c r="E80">
+        <v>26899866</v>
+      </c>
+      <c r="F80">
+        <v>16149568</v>
+      </c>
+      <c r="G80">
+        <v>3925959</v>
+      </c>
+      <c r="H80">
+        <v>6756698</v>
+      </c>
+      <c r="I80">
+        <v>67641</v>
+      </c>
+      <c r="J80">
+        <v>6367025</v>
+      </c>
+      <c r="K80">
+        <v>33266891</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81">
+        <v>27080023</v>
+      </c>
+      <c r="C81">
+        <v>5921112</v>
+      </c>
+      <c r="D81">
+        <v>33001135</v>
+      </c>
+      <c r="E81">
+        <v>26965278</v>
+      </c>
+      <c r="F81">
+        <v>16186221</v>
+      </c>
+      <c r="G81">
+        <v>3916066</v>
+      </c>
+      <c r="H81">
+        <v>6690800</v>
+      </c>
+      <c r="I81">
+        <v>172191</v>
+      </c>
+      <c r="J81">
+        <v>6035857</v>
+      </c>
+      <c r="K81">
+        <v>33001135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82">
+        <v>26250834</v>
+      </c>
+      <c r="C82">
+        <v>5664014</v>
+      </c>
+      <c r="D82">
+        <v>31914848</v>
+      </c>
+      <c r="E82">
+        <v>26026642</v>
+      </c>
+      <c r="F82">
+        <v>15817602</v>
+      </c>
+      <c r="G82">
+        <v>3831586</v>
+      </c>
+      <c r="H82">
+        <v>6329821</v>
+      </c>
+      <c r="I82">
+        <v>47633</v>
+      </c>
+      <c r="J82">
+        <v>5888206</v>
+      </c>
+      <c r="K82">
+        <v>31914848</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83">
+        <v>23544804</v>
+      </c>
+      <c r="C83">
+        <v>4596256</v>
+      </c>
+      <c r="D83">
+        <v>28141060</v>
+      </c>
+      <c r="E83">
+        <v>23108821</v>
+      </c>
+      <c r="F83">
+        <v>14313647</v>
+      </c>
+      <c r="G83">
+        <v>3544477</v>
+      </c>
+      <c r="H83">
+        <v>5359187</v>
+      </c>
+      <c r="I83">
+        <v>-108490</v>
+      </c>
+      <c r="J83">
+        <v>5032239</v>
+      </c>
+      <c r="K83">
+        <v>28141060</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84">
+        <v>24331550</v>
+      </c>
+      <c r="C84">
+        <v>4748278</v>
+      </c>
+      <c r="D84">
+        <v>29079828</v>
+      </c>
+      <c r="E84">
+        <v>23609106</v>
+      </c>
+      <c r="F84">
+        <v>14616999</v>
+      </c>
+      <c r="G84">
+        <v>3556210</v>
+      </c>
+      <c r="H84">
+        <v>5716201</v>
+      </c>
+      <c r="I84">
+        <v>-280304</v>
+      </c>
+      <c r="J84">
+        <v>5470722</v>
+      </c>
+      <c r="K84">
+        <v>29079828</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85">
+        <v>24680822</v>
+      </c>
+      <c r="C85">
+        <v>5497510</v>
+      </c>
+      <c r="D85">
+        <v>30178332</v>
+      </c>
+      <c r="E85">
+        <v>24305504</v>
+      </c>
+      <c r="F85">
+        <v>14973720</v>
+      </c>
+      <c r="G85">
+        <v>3553932</v>
+      </c>
+      <c r="H85">
+        <v>5847369</v>
+      </c>
+      <c r="I85">
+        <v>-69517</v>
+      </c>
+      <c r="J85">
+        <v>5872828</v>
+      </c>
+      <c r="K85">
+        <v>30178332</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{103AA3FF-87A9-3E4F-8E35-02A86275B0FB}">
+  <dimension ref="A1:K85"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>9134587</v>
+      </c>
+      <c r="C2">
+        <v>1670064</v>
+      </c>
+      <c r="D2">
+        <v>10804651</v>
+      </c>
+      <c r="E2">
+        <v>8010469</v>
+      </c>
+      <c r="F2">
+        <v>5611570</v>
+      </c>
+      <c r="G2">
+        <v>1141204</v>
+      </c>
+      <c r="H2">
+        <v>1324528</v>
+      </c>
+      <c r="I2">
+        <v>-66833</v>
+      </c>
+      <c r="J2">
+        <v>2794182</v>
+      </c>
+      <c r="K2">
+        <v>10804651</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>9320414</v>
+      </c>
+      <c r="C3">
+        <v>1704978</v>
+      </c>
+      <c r="D3">
+        <v>11025392</v>
+      </c>
+      <c r="E3">
+        <v>8198851</v>
+      </c>
+      <c r="F3">
+        <v>5728145</v>
+      </c>
+      <c r="G3">
+        <v>1159906</v>
+      </c>
+      <c r="H3">
+        <v>1403726</v>
+      </c>
+      <c r="I3">
+        <v>-92926</v>
+      </c>
+      <c r="J3">
+        <v>2826541</v>
+      </c>
+      <c r="K3">
+        <v>11025392</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>9548491</v>
+      </c>
+      <c r="C4">
+        <v>1863174</v>
+      </c>
+      <c r="D4">
+        <v>11411665</v>
+      </c>
+      <c r="E4">
+        <v>8579409</v>
+      </c>
+      <c r="F4">
+        <v>5846313</v>
+      </c>
+      <c r="G4">
+        <v>1180131</v>
+      </c>
+      <c r="H4">
+        <v>1499091</v>
+      </c>
+      <c r="I4">
+        <v>53874</v>
+      </c>
+      <c r="J4">
+        <v>2832256</v>
+      </c>
+      <c r="K4">
+        <v>11411665</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>9722918</v>
+      </c>
+      <c r="C5">
+        <v>2069367</v>
+      </c>
+      <c r="D5">
+        <v>11792285</v>
+      </c>
+      <c r="E5">
+        <v>8996834</v>
+      </c>
+      <c r="F5">
+        <v>5980511</v>
+      </c>
+      <c r="G5">
+        <v>1210666</v>
+      </c>
+      <c r="H5">
+        <v>1626448</v>
+      </c>
+      <c r="I5">
+        <v>179209</v>
+      </c>
+      <c r="J5">
+        <v>2795451</v>
+      </c>
+      <c r="K5">
+        <v>11792285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>9699363</v>
+      </c>
+      <c r="C6">
+        <v>2260771</v>
+      </c>
+      <c r="D6">
+        <v>11960134</v>
+      </c>
+      <c r="E6">
+        <v>9125177</v>
+      </c>
+      <c r="F6">
+        <v>6121143</v>
+      </c>
+      <c r="G6">
+        <v>1124607</v>
+      </c>
+      <c r="H6">
+        <v>1683228</v>
+      </c>
+      <c r="I6">
+        <v>196199</v>
+      </c>
+      <c r="J6">
+        <v>2834957</v>
+      </c>
+      <c r="K6">
+        <v>11960134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>9802413</v>
+      </c>
+      <c r="C7">
+        <v>2205560</v>
+      </c>
+      <c r="D7">
+        <v>12007973</v>
+      </c>
+      <c r="E7">
+        <v>9226563</v>
+      </c>
+      <c r="F7">
+        <v>6179534</v>
+      </c>
+      <c r="G7">
+        <v>1134726</v>
+      </c>
+      <c r="H7">
+        <v>1719092</v>
+      </c>
+      <c r="I7">
+        <v>193211</v>
+      </c>
+      <c r="J7">
+        <v>2781410</v>
+      </c>
+      <c r="K7">
+        <v>12007973</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>9809483</v>
+      </c>
+      <c r="C8">
+        <v>2274274</v>
+      </c>
+      <c r="D8">
+        <v>12083757</v>
+      </c>
+      <c r="E8">
+        <v>9356325</v>
+      </c>
+      <c r="F8">
+        <v>6229424</v>
+      </c>
+      <c r="G8">
+        <v>1130148</v>
+      </c>
+      <c r="H8">
+        <v>1782603</v>
+      </c>
+      <c r="I8">
+        <v>214150</v>
+      </c>
+      <c r="J8">
+        <v>2727432</v>
+      </c>
+      <c r="K8">
+        <v>12083757</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>9930104</v>
+      </c>
+      <c r="C9">
+        <v>2446663</v>
+      </c>
+      <c r="D9">
+        <v>12376767</v>
+      </c>
+      <c r="E9">
+        <v>9650666</v>
+      </c>
+      <c r="F9">
+        <v>6369298</v>
+      </c>
+      <c r="G9">
+        <v>1146491</v>
+      </c>
+      <c r="H9">
+        <v>1854631</v>
+      </c>
+      <c r="I9">
+        <v>280246</v>
+      </c>
+      <c r="J9">
+        <v>2726101</v>
+      </c>
+      <c r="K9">
+        <v>12376767</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>10063566</v>
+      </c>
+      <c r="C10">
+        <v>2870923</v>
+      </c>
+      <c r="D10">
+        <v>12934489</v>
+      </c>
+      <c r="E10">
+        <v>10214852</v>
+      </c>
+      <c r="F10">
+        <v>6563537</v>
+      </c>
+      <c r="G10">
+        <v>1149300</v>
+      </c>
+      <c r="H10">
+        <v>2132387</v>
+      </c>
+      <c r="I10">
+        <v>369628</v>
+      </c>
+      <c r="J10">
+        <v>2719637</v>
+      </c>
+      <c r="K10">
+        <v>12934489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>10205818</v>
+      </c>
+      <c r="C11">
+        <v>2778136</v>
+      </c>
+      <c r="D11">
+        <v>12983954</v>
+      </c>
+      <c r="E11">
+        <v>10151057</v>
+      </c>
+      <c r="F11">
+        <v>6627661</v>
+      </c>
+      <c r="G11">
+        <v>1156927</v>
+      </c>
+      <c r="H11">
+        <v>2050561</v>
+      </c>
+      <c r="I11">
+        <v>315908</v>
+      </c>
+      <c r="J11">
+        <v>2832897</v>
+      </c>
+      <c r="K11">
+        <v>12983954</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>10274208</v>
+      </c>
+      <c r="C12">
+        <v>2673863</v>
+      </c>
+      <c r="D12">
+        <v>12948071</v>
+      </c>
+      <c r="E12">
+        <v>10128016</v>
+      </c>
+      <c r="F12">
+        <v>6714019</v>
+      </c>
+      <c r="G12">
+        <v>1163350</v>
+      </c>
+      <c r="H12">
+        <v>2052365</v>
+      </c>
+      <c r="I12">
+        <v>198282</v>
+      </c>
+      <c r="J12">
+        <v>2820055</v>
+      </c>
+      <c r="K12">
+        <v>12948071</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>10305402</v>
+      </c>
+      <c r="C13">
+        <v>2611304</v>
+      </c>
+      <c r="D13">
+        <v>12916706</v>
+      </c>
+      <c r="E13">
+        <v>10150343</v>
+      </c>
+      <c r="F13">
+        <v>6756119</v>
+      </c>
+      <c r="G13">
+        <v>1173595</v>
+      </c>
+      <c r="H13">
+        <v>2077857</v>
+      </c>
+      <c r="I13">
+        <v>142772</v>
+      </c>
+      <c r="J13">
+        <v>2766363</v>
+      </c>
+      <c r="K13">
+        <v>12916706</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>10440088</v>
+      </c>
+      <c r="C14">
+        <v>2933578</v>
+      </c>
+      <c r="D14">
+        <v>13373666</v>
+      </c>
+      <c r="E14">
+        <v>10589475</v>
+      </c>
+      <c r="F14">
+        <v>6963349</v>
+      </c>
+      <c r="G14">
+        <v>1152356</v>
+      </c>
+      <c r="H14">
+        <v>2301805</v>
+      </c>
+      <c r="I14">
+        <v>171965</v>
+      </c>
+      <c r="J14">
+        <v>2784191</v>
+      </c>
+      <c r="K14">
+        <v>13373666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>10240791</v>
+      </c>
+      <c r="C15">
+        <v>2638740</v>
+      </c>
+      <c r="D15">
+        <v>12879531</v>
+      </c>
+      <c r="E15">
+        <v>10041688</v>
+      </c>
+      <c r="F15">
+        <v>6879152</v>
+      </c>
+      <c r="G15">
+        <v>1167376</v>
+      </c>
+      <c r="H15">
+        <v>2090062</v>
+      </c>
+      <c r="I15">
+        <v>-94902</v>
+      </c>
+      <c r="J15">
+        <v>2837843</v>
+      </c>
+      <c r="K15">
+        <v>12879531</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>10464381</v>
+      </c>
+      <c r="C16">
+        <v>2468818</v>
+      </c>
+      <c r="D16">
+        <v>12933199</v>
+      </c>
+      <c r="E16">
+        <v>9898383</v>
+      </c>
+      <c r="F16">
+        <v>6817149</v>
+      </c>
+      <c r="G16">
+        <v>1180502</v>
+      </c>
+      <c r="H16">
+        <v>1974975</v>
+      </c>
+      <c r="I16">
+        <v>-74243</v>
+      </c>
+      <c r="J16">
+        <v>3034816</v>
+      </c>
+      <c r="K16">
+        <v>12933199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>10816002</v>
+      </c>
+      <c r="C17">
+        <v>2449195</v>
+      </c>
+      <c r="D17">
+        <v>13265197</v>
+      </c>
+      <c r="E17">
+        <v>9979957</v>
+      </c>
+      <c r="F17">
+        <v>6801939</v>
+      </c>
+      <c r="G17">
+        <v>1196468</v>
+      </c>
+      <c r="H17">
+        <v>1977666</v>
+      </c>
+      <c r="I17">
+        <v>3884</v>
+      </c>
+      <c r="J17">
+        <v>3285240</v>
+      </c>
+      <c r="K17">
+        <v>13265197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>11091411</v>
+      </c>
+      <c r="C18">
+        <v>2871890</v>
+      </c>
+      <c r="D18">
+        <v>13963301</v>
+      </c>
+      <c r="E18">
+        <v>10680681</v>
+      </c>
+      <c r="F18">
+        <v>7210235</v>
+      </c>
+      <c r="G18">
+        <v>1209014</v>
+      </c>
+      <c r="H18">
+        <v>2195853</v>
+      </c>
+      <c r="I18">
+        <v>65579</v>
+      </c>
+      <c r="J18">
+        <v>3282620</v>
+      </c>
+      <c r="K18">
+        <v>13963301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>11282549</v>
+      </c>
+      <c r="C19">
+        <v>2803313</v>
+      </c>
+      <c r="D19">
+        <v>14085862</v>
+      </c>
+      <c r="E19">
+        <v>10534842</v>
+      </c>
+      <c r="F19">
+        <v>7189610</v>
+      </c>
+      <c r="G19">
+        <v>1222907</v>
+      </c>
+      <c r="H19">
+        <v>2151597</v>
+      </c>
+      <c r="I19">
+        <v>-29272</v>
+      </c>
+      <c r="J19">
+        <v>3551020</v>
+      </c>
+      <c r="K19">
+        <v>14085862</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>11403289</v>
+      </c>
+      <c r="C20">
+        <v>2913380</v>
+      </c>
+      <c r="D20">
+        <v>14316669</v>
+      </c>
+      <c r="E20">
+        <v>10742765</v>
+      </c>
+      <c r="F20">
+        <v>7326390</v>
+      </c>
+      <c r="G20">
+        <v>1233879</v>
+      </c>
+      <c r="H20">
+        <v>2176673</v>
+      </c>
+      <c r="I20">
+        <v>5823</v>
+      </c>
+      <c r="J20">
+        <v>3573904</v>
+      </c>
+      <c r="K20">
+        <v>14316669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>11629461</v>
+      </c>
+      <c r="C21">
+        <v>3042771</v>
+      </c>
+      <c r="D21">
+        <v>14672232</v>
+      </c>
+      <c r="E21">
+        <v>11086229</v>
+      </c>
+      <c r="F21">
+        <v>7502734</v>
+      </c>
+      <c r="G21">
+        <v>1241345</v>
+      </c>
+      <c r="H21">
+        <v>2261008</v>
+      </c>
+      <c r="I21">
+        <v>81142</v>
+      </c>
+      <c r="J21">
+        <v>3586003</v>
+      </c>
+      <c r="K21">
+        <v>14672232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>11771814</v>
+      </c>
+      <c r="C22">
+        <v>3369653</v>
+      </c>
+      <c r="D22">
+        <v>15141467</v>
+      </c>
+      <c r="E22">
+        <v>11409939</v>
+      </c>
+      <c r="F22">
+        <v>7501717</v>
+      </c>
+      <c r="G22">
+        <v>1270742</v>
+      </c>
+      <c r="H22">
+        <v>2420343</v>
+      </c>
+      <c r="I22">
+        <v>217137</v>
+      </c>
+      <c r="J22">
+        <v>3731528</v>
+      </c>
+      <c r="K22">
+        <v>15141467</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>11936392</v>
+      </c>
+      <c r="C23">
+        <v>3398718</v>
+      </c>
+      <c r="D23">
+        <v>15335110</v>
+      </c>
+      <c r="E23">
+        <v>11541784</v>
+      </c>
+      <c r="F23">
+        <v>7619513</v>
+      </c>
+      <c r="G23">
+        <v>1260510</v>
+      </c>
+      <c r="H23">
+        <v>2489052</v>
+      </c>
+      <c r="I23">
+        <v>172709</v>
+      </c>
+      <c r="J23">
+        <v>3793326</v>
+      </c>
+      <c r="K23">
+        <v>15335110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>11951919</v>
+      </c>
+      <c r="C24">
+        <v>3213563</v>
+      </c>
+      <c r="D24">
+        <v>15165482</v>
+      </c>
+      <c r="E24">
+        <v>11358821</v>
+      </c>
+      <c r="F24">
+        <v>7634650</v>
+      </c>
+      <c r="G24">
+        <v>1271608</v>
+      </c>
+      <c r="H24">
+        <v>2413061</v>
+      </c>
+      <c r="I24">
+        <v>39502</v>
+      </c>
+      <c r="J24">
+        <v>3806661</v>
+      </c>
+      <c r="K24">
+        <v>15165482</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>12149194</v>
+      </c>
+      <c r="C25">
+        <v>3323793</v>
+      </c>
+      <c r="D25">
+        <v>15472987</v>
+      </c>
+      <c r="E25">
+        <v>11602887</v>
+      </c>
+      <c r="F25">
+        <v>7767261</v>
+      </c>
+      <c r="G25">
+        <v>1278530</v>
+      </c>
+      <c r="H25">
+        <v>2406536</v>
+      </c>
+      <c r="I25">
+        <v>150560</v>
+      </c>
+      <c r="J25">
+        <v>3870100</v>
+      </c>
+      <c r="K25">
+        <v>15472987</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>12278116</v>
+      </c>
+      <c r="C26">
+        <v>3667057</v>
+      </c>
+      <c r="D26">
+        <v>15945173</v>
+      </c>
+      <c r="E26">
+        <v>11909990</v>
+      </c>
+      <c r="F26">
+        <v>7846653</v>
+      </c>
+      <c r="G26">
+        <v>1282502</v>
+      </c>
+      <c r="H26">
+        <v>2584061</v>
+      </c>
+      <c r="I26">
+        <v>196774</v>
+      </c>
+      <c r="J26">
+        <v>4035183</v>
+      </c>
+      <c r="K26">
+        <v>15945173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>12447026</v>
+      </c>
+      <c r="C27">
+        <v>3649214</v>
+      </c>
+      <c r="D27">
+        <v>16096240</v>
+      </c>
+      <c r="E27">
+        <v>12025242</v>
+      </c>
+      <c r="F27">
+        <v>7925244</v>
+      </c>
+      <c r="G27">
+        <v>1297992</v>
+      </c>
+      <c r="H27">
+        <v>2564933</v>
+      </c>
+      <c r="I27">
+        <v>237073</v>
+      </c>
+      <c r="J27">
+        <v>4070998</v>
+      </c>
+      <c r="K27">
+        <v>16096240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>12592998</v>
+      </c>
+      <c r="C28">
+        <v>3613860</v>
+      </c>
+      <c r="D28">
+        <v>16206858</v>
+      </c>
+      <c r="E28">
+        <v>12159542</v>
+      </c>
+      <c r="F28">
+        <v>7992370</v>
+      </c>
+      <c r="G28">
+        <v>1321123</v>
+      </c>
+      <c r="H28">
+        <v>2551535</v>
+      </c>
+      <c r="I28">
+        <v>294514</v>
+      </c>
+      <c r="J28">
+        <v>4047316</v>
+      </c>
+      <c r="K28">
+        <v>16206858</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>12596475</v>
+      </c>
+      <c r="C29">
+        <v>3676033</v>
+      </c>
+      <c r="D29">
+        <v>16272508</v>
+      </c>
+      <c r="E29">
+        <v>12141123</v>
+      </c>
+      <c r="F29">
+        <v>8087266</v>
+      </c>
+      <c r="G29">
+        <v>1372615</v>
+      </c>
+      <c r="H29">
+        <v>2513289</v>
+      </c>
+      <c r="I29">
+        <v>167953</v>
+      </c>
+      <c r="J29">
+        <v>4131385</v>
+      </c>
+      <c r="K29">
+        <v>16272508</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>12548685</v>
+      </c>
+      <c r="C30">
+        <v>3984250</v>
+      </c>
+      <c r="D30">
+        <v>16532935</v>
+      </c>
+      <c r="E30">
+        <v>12563850</v>
+      </c>
+      <c r="F30">
+        <v>8183831</v>
+      </c>
+      <c r="G30">
+        <v>1392154</v>
+      </c>
+      <c r="H30">
+        <v>2723245</v>
+      </c>
+      <c r="I30">
+        <v>264620</v>
+      </c>
+      <c r="J30">
+        <v>3969085</v>
+      </c>
+      <c r="K30">
+        <v>16532935</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>12641374</v>
+      </c>
+      <c r="C31">
+        <v>3847272</v>
+      </c>
+      <c r="D31">
+        <v>16488646</v>
+      </c>
+      <c r="E31">
+        <v>12483042</v>
+      </c>
+      <c r="F31">
+        <v>8224323</v>
+      </c>
+      <c r="G31">
+        <v>1430188</v>
+      </c>
+      <c r="H31">
+        <v>2616530</v>
+      </c>
+      <c r="I31">
+        <v>212001</v>
+      </c>
+      <c r="J31">
+        <v>4005604</v>
+      </c>
+      <c r="K31">
+        <v>16488646</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>12821498</v>
+      </c>
+      <c r="C32">
+        <v>3901662</v>
+      </c>
+      <c r="D32">
+        <v>16723160</v>
+      </c>
+      <c r="E32">
+        <v>12540742</v>
+      </c>
+      <c r="F32">
+        <v>8350010</v>
+      </c>
+      <c r="G32">
+        <v>1391983</v>
+      </c>
+      <c r="H32">
+        <v>2602698</v>
+      </c>
+      <c r="I32">
+        <v>196051</v>
+      </c>
+      <c r="J32">
+        <v>4182418</v>
+      </c>
+      <c r="K32">
+        <v>16723160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>12996220</v>
+      </c>
+      <c r="C33">
+        <v>3903439</v>
+      </c>
+      <c r="D33">
+        <v>16899659</v>
+      </c>
+      <c r="E33">
+        <v>12769081</v>
+      </c>
+      <c r="F33">
+        <v>8443114</v>
+      </c>
+      <c r="G33">
+        <v>1359884</v>
+      </c>
+      <c r="H33">
+        <v>2651474</v>
+      </c>
+      <c r="I33">
+        <v>314609</v>
+      </c>
+      <c r="J33">
+        <v>4130578</v>
+      </c>
+      <c r="K33">
+        <v>16899659</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>13203590</v>
+      </c>
+      <c r="C34">
+        <v>4405473</v>
+      </c>
+      <c r="D34">
+        <v>17609063</v>
+      </c>
+      <c r="E34">
+        <v>13334287</v>
+      </c>
+      <c r="F34">
+        <v>8504226</v>
+      </c>
+      <c r="G34">
+        <v>1507869</v>
+      </c>
+      <c r="H34">
+        <v>2879303</v>
+      </c>
+      <c r="I34">
+        <v>442889</v>
+      </c>
+      <c r="J34">
+        <v>4274776</v>
+      </c>
+      <c r="K34">
+        <v>17609063</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>13437956</v>
+      </c>
+      <c r="C35">
+        <v>4563811</v>
+      </c>
+      <c r="D35">
+        <v>18001767</v>
+      </c>
+      <c r="E35">
+        <v>13715669</v>
+      </c>
+      <c r="F35">
+        <v>8702404</v>
+      </c>
+      <c r="G35">
+        <v>1533769</v>
+      </c>
+      <c r="H35">
+        <v>2978775</v>
+      </c>
+      <c r="I35">
+        <v>500721</v>
+      </c>
+      <c r="J35">
+        <v>4286098</v>
+      </c>
+      <c r="K35">
+        <v>18001767</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>13689235</v>
+      </c>
+      <c r="C36">
+        <v>4566615</v>
+      </c>
+      <c r="D36">
+        <v>18255850</v>
+      </c>
+      <c r="E36">
+        <v>14137078</v>
+      </c>
+      <c r="F36">
+        <v>8843861</v>
+      </c>
+      <c r="G36">
+        <v>1567409</v>
+      </c>
+      <c r="H36">
+        <v>3147200</v>
+      </c>
+      <c r="I36">
+        <v>578608</v>
+      </c>
+      <c r="J36">
+        <v>4118772</v>
+      </c>
+      <c r="K36">
+        <v>18255850</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>13919627</v>
+      </c>
+      <c r="C37">
+        <v>4358529</v>
+      </c>
+      <c r="D37">
+        <v>18278156</v>
+      </c>
+      <c r="E37">
+        <v>14184101</v>
+      </c>
+      <c r="F37">
+        <v>8944365</v>
+      </c>
+      <c r="G37">
+        <v>1582301</v>
+      </c>
+      <c r="H37">
+        <v>3280937</v>
+      </c>
+      <c r="I37">
+        <v>376498</v>
+      </c>
+      <c r="J37">
+        <v>4094055</v>
+      </c>
+      <c r="K37">
+        <v>18278156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>13721197</v>
+      </c>
+      <c r="C38">
+        <v>4096763</v>
+      </c>
+      <c r="D38">
+        <v>17817960</v>
+      </c>
+      <c r="E38">
+        <v>13839148</v>
+      </c>
+      <c r="F38">
+        <v>8684315</v>
+      </c>
+      <c r="G38">
+        <v>1649246</v>
+      </c>
+      <c r="H38">
+        <v>3116030</v>
+      </c>
+      <c r="I38">
+        <v>389557</v>
+      </c>
+      <c r="J38">
+        <v>3978812</v>
+      </c>
+      <c r="K38">
+        <v>17817960</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>13663730</v>
+      </c>
+      <c r="C39">
+        <v>3864607</v>
+      </c>
+      <c r="D39">
+        <v>17528337</v>
+      </c>
+      <c r="E39">
+        <v>13595043</v>
+      </c>
+      <c r="F39">
+        <v>8580608</v>
+      </c>
+      <c r="G39">
+        <v>1694034</v>
+      </c>
+      <c r="H39">
+        <v>2936507</v>
+      </c>
+      <c r="I39">
+        <v>383894</v>
+      </c>
+      <c r="J39">
+        <v>3933294</v>
+      </c>
+      <c r="K39">
+        <v>17528337</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>13579505</v>
+      </c>
+      <c r="C40">
+        <v>3916485</v>
+      </c>
+      <c r="D40">
+        <v>17495990</v>
+      </c>
+      <c r="E40">
+        <v>13450642</v>
+      </c>
+      <c r="F40">
+        <v>8624846</v>
+      </c>
+      <c r="G40">
+        <v>1763779</v>
+      </c>
+      <c r="H40">
+        <v>2886989</v>
+      </c>
+      <c r="I40">
+        <v>175028</v>
+      </c>
+      <c r="J40">
+        <v>4045348</v>
+      </c>
+      <c r="K40">
+        <v>17495990</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>13593300</v>
+      </c>
+      <c r="C41">
+        <v>4241573</v>
+      </c>
+      <c r="D41">
+        <v>17834873</v>
+      </c>
+      <c r="E41">
+        <v>13821809</v>
+      </c>
+      <c r="F41">
+        <v>8758627</v>
+      </c>
+      <c r="G41">
+        <v>1803195</v>
+      </c>
+      <c r="H41">
+        <v>2903803</v>
+      </c>
+      <c r="I41">
+        <v>356184</v>
+      </c>
+      <c r="J41">
+        <v>4013064</v>
+      </c>
+      <c r="K41">
+        <v>17834873</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>13729815</v>
+      </c>
+      <c r="C42">
+        <v>4455065</v>
+      </c>
+      <c r="D42">
+        <v>18184880</v>
+      </c>
+      <c r="E42">
+        <v>14236869</v>
+      </c>
+      <c r="F42">
+        <v>9114070</v>
+      </c>
+      <c r="G42">
+        <v>1775081</v>
+      </c>
+      <c r="H42">
+        <v>3090304</v>
+      </c>
+      <c r="I42">
+        <v>257414</v>
+      </c>
+      <c r="J42">
+        <v>3948011</v>
+      </c>
+      <c r="K42">
+        <v>18184880</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>13946256</v>
+      </c>
+      <c r="C43">
+        <v>4662061</v>
+      </c>
+      <c r="D43">
+        <v>18608317</v>
+      </c>
+      <c r="E43">
+        <v>14547615</v>
+      </c>
+      <c r="F43">
+        <v>9262431</v>
+      </c>
+      <c r="G43">
+        <v>1770696</v>
+      </c>
+      <c r="H43">
+        <v>3213729</v>
+      </c>
+      <c r="I43">
+        <v>300759</v>
+      </c>
+      <c r="J43">
+        <v>4060702</v>
+      </c>
+      <c r="K43">
+        <v>18608317</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>14175891</v>
+      </c>
+      <c r="C44">
+        <v>4695215</v>
+      </c>
+      <c r="D44">
+        <v>18871106</v>
+      </c>
+      <c r="E44">
+        <v>14985244</v>
+      </c>
+      <c r="F44">
+        <v>9392453</v>
+      </c>
+      <c r="G44">
+        <v>1806521</v>
+      </c>
+      <c r="H44">
+        <v>3316643</v>
+      </c>
+      <c r="I44">
+        <v>469627</v>
+      </c>
+      <c r="J44">
+        <v>3885862</v>
+      </c>
+      <c r="K44">
+        <v>18871106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>14629093</v>
+      </c>
+      <c r="C45">
+        <v>4696647</v>
+      </c>
+      <c r="D45">
+        <v>19325740</v>
+      </c>
+      <c r="E45">
+        <v>15287658</v>
+      </c>
+      <c r="F45">
+        <v>9551681</v>
+      </c>
+      <c r="G45">
+        <v>1861207</v>
+      </c>
+      <c r="H45">
+        <v>3429472</v>
+      </c>
+      <c r="I45">
+        <v>445298</v>
+      </c>
+      <c r="J45">
+        <v>4038082</v>
+      </c>
+      <c r="K45">
+        <v>19325740</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>14790364</v>
+      </c>
+      <c r="C46">
+        <v>4763357</v>
+      </c>
+      <c r="D46">
+        <v>19553721</v>
+      </c>
+      <c r="E46">
+        <v>15411649</v>
+      </c>
+      <c r="F46">
+        <v>9628347</v>
+      </c>
+      <c r="G46">
+        <v>1873436</v>
+      </c>
+      <c r="H46">
+        <v>3569862</v>
+      </c>
+      <c r="I46">
+        <v>340004</v>
+      </c>
+      <c r="J46">
+        <v>4142072</v>
+      </c>
+      <c r="K46">
+        <v>19553721</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>15176741</v>
+      </c>
+      <c r="C47">
+        <v>4754509</v>
+      </c>
+      <c r="D47">
+        <v>19931250</v>
+      </c>
+      <c r="E47">
+        <v>15795867</v>
+      </c>
+      <c r="F47">
+        <v>9766589</v>
+      </c>
+      <c r="G47">
+        <v>1975903</v>
+      </c>
+      <c r="H47">
+        <v>3667959</v>
+      </c>
+      <c r="I47">
+        <v>385416</v>
+      </c>
+      <c r="J47">
+        <v>4135383</v>
+      </c>
+      <c r="K47">
+        <v>19931250</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>15409103</v>
+      </c>
+      <c r="C48">
+        <v>4819918</v>
+      </c>
+      <c r="D48">
+        <v>20229021</v>
+      </c>
+      <c r="E48">
+        <v>15949444</v>
+      </c>
+      <c r="F48">
+        <v>9884927</v>
+      </c>
+      <c r="G48">
+        <v>1969328</v>
+      </c>
+      <c r="H48">
+        <v>3787621</v>
+      </c>
+      <c r="I48">
+        <v>307568</v>
+      </c>
+      <c r="J48">
+        <v>4279577</v>
+      </c>
+      <c r="K48">
+        <v>20229021</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>15548856</v>
+      </c>
+      <c r="C49">
+        <v>4846119</v>
+      </c>
+      <c r="D49">
+        <v>20394975</v>
+      </c>
+      <c r="E49">
+        <v>16116325</v>
+      </c>
+      <c r="F49">
+        <v>9954766</v>
+      </c>
+      <c r="G49">
+        <v>2022215</v>
+      </c>
+      <c r="H49">
+        <v>3895349</v>
+      </c>
+      <c r="I49">
+        <v>243995</v>
+      </c>
+      <c r="J49">
+        <v>4278650</v>
+      </c>
+      <c r="K49">
+        <v>20394975</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>15798590</v>
+      </c>
+      <c r="C50">
+        <v>4762891</v>
+      </c>
+      <c r="D50">
+        <v>20561481</v>
+      </c>
+      <c r="E50">
+        <v>16167679</v>
+      </c>
+      <c r="F50">
+        <v>9925286</v>
+      </c>
+      <c r="G50">
+        <v>2126916</v>
+      </c>
+      <c r="H50">
+        <v>3994847</v>
+      </c>
+      <c r="I50">
+        <v>120630</v>
+      </c>
+      <c r="J50">
+        <v>4393802</v>
+      </c>
+      <c r="K50">
+        <v>20561481</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>16072842</v>
+      </c>
+      <c r="C51">
+        <v>4817886</v>
+      </c>
+      <c r="D51">
+        <v>20890728</v>
+      </c>
+      <c r="E51">
+        <v>16418791</v>
+      </c>
+      <c r="F51">
+        <v>10092714</v>
+      </c>
+      <c r="G51">
+        <v>2132933</v>
+      </c>
+      <c r="H51">
+        <v>4094112</v>
+      </c>
+      <c r="I51">
+        <v>99032</v>
+      </c>
+      <c r="J51">
+        <v>4471937</v>
+      </c>
+      <c r="K51">
+        <v>20890728</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>16196959</v>
+      </c>
+      <c r="C52">
+        <v>4904123</v>
+      </c>
+      <c r="D52">
+        <v>21101082</v>
+      </c>
+      <c r="E52">
+        <v>16652906</v>
+      </c>
+      <c r="F52">
+        <v>10142977</v>
+      </c>
+      <c r="G52">
+        <v>2180245</v>
+      </c>
+      <c r="H52">
+        <v>4188875</v>
+      </c>
+      <c r="I52">
+        <v>140809</v>
+      </c>
+      <c r="J52">
+        <v>4448176</v>
+      </c>
+      <c r="K52">
+        <v>21101082</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>16294042</v>
+      </c>
+      <c r="C53">
+        <v>4859162</v>
+      </c>
+      <c r="D53">
+        <v>21153204</v>
+      </c>
+      <c r="E53">
+        <v>16711101</v>
+      </c>
+      <c r="F53">
+        <v>10200903</v>
+      </c>
+      <c r="G53">
+        <v>2271998</v>
+      </c>
+      <c r="H53">
+        <v>4218334</v>
+      </c>
+      <c r="I53">
+        <v>19866</v>
+      </c>
+      <c r="J53">
+        <v>4442103</v>
+      </c>
+      <c r="K53">
+        <v>21153204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>16458713</v>
+      </c>
+      <c r="C54">
+        <v>5134397</v>
+      </c>
+      <c r="D54">
+        <v>21593110</v>
+      </c>
+      <c r="E54">
+        <v>17173706</v>
+      </c>
+      <c r="F54">
+        <v>10294947</v>
+      </c>
+      <c r="G54">
+        <v>2352232</v>
+      </c>
+      <c r="H54">
+        <v>4456627</v>
+      </c>
+      <c r="I54">
+        <v>69900</v>
+      </c>
+      <c r="J54">
+        <v>4419404</v>
+      </c>
+      <c r="K54">
+        <v>21593110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>16802240</v>
+      </c>
+      <c r="C55">
+        <v>5332142</v>
+      </c>
+      <c r="D55">
+        <v>22134382</v>
+      </c>
+      <c r="E55">
+        <v>17609324</v>
+      </c>
+      <c r="F55">
+        <v>10526381</v>
+      </c>
+      <c r="G55">
+        <v>2401796</v>
+      </c>
+      <c r="H55">
+        <v>4576320</v>
+      </c>
+      <c r="I55">
+        <v>104827</v>
+      </c>
+      <c r="J55">
+        <v>4525058</v>
+      </c>
+      <c r="K55">
+        <v>22134382</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>17131619</v>
+      </c>
+      <c r="C56">
+        <v>5220815</v>
+      </c>
+      <c r="D56">
+        <v>22352434</v>
+      </c>
+      <c r="E56">
+        <v>17740362</v>
+      </c>
+      <c r="F56">
+        <v>10535794</v>
+      </c>
+      <c r="G56">
+        <v>2433480</v>
+      </c>
+      <c r="H56">
+        <v>4624561</v>
+      </c>
+      <c r="I56">
+        <v>146527</v>
+      </c>
+      <c r="J56">
+        <v>4612072</v>
+      </c>
+      <c r="K56">
+        <v>22352434</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>17153556</v>
+      </c>
+      <c r="C57">
+        <v>5004209</v>
+      </c>
+      <c r="D57">
+        <v>22157765</v>
+      </c>
+      <c r="E57">
+        <v>17504019</v>
+      </c>
+      <c r="F57">
+        <v>10585156</v>
+      </c>
+      <c r="G57">
+        <v>2422255</v>
+      </c>
+      <c r="H57">
+        <v>4556586</v>
+      </c>
+      <c r="I57">
+        <v>-59978</v>
+      </c>
+      <c r="J57">
+        <v>4653746</v>
+      </c>
+      <c r="K57">
+        <v>22157765</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>17096076</v>
+      </c>
+      <c r="C58">
+        <v>5071785</v>
+      </c>
+      <c r="D58">
+        <v>22167861</v>
+      </c>
+      <c r="E58">
+        <v>17490040</v>
+      </c>
+      <c r="F58">
+        <v>10491498</v>
+      </c>
+      <c r="G58">
+        <v>2402505</v>
+      </c>
+      <c r="H58">
+        <v>4507001</v>
+      </c>
+      <c r="I58">
+        <v>89036</v>
+      </c>
+      <c r="J58">
+        <v>4677821</v>
+      </c>
+      <c r="K58">
+        <v>22167861</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>17494063</v>
+      </c>
+      <c r="C59">
+        <v>5394893</v>
+      </c>
+      <c r="D59">
+        <v>22888956</v>
+      </c>
+      <c r="E59">
+        <v>18033006</v>
+      </c>
+      <c r="F59">
+        <v>10734866</v>
+      </c>
+      <c r="G59">
+        <v>2568536</v>
+      </c>
+      <c r="H59">
+        <v>4574171</v>
+      </c>
+      <c r="I59">
+        <v>155433</v>
+      </c>
+      <c r="J59">
+        <v>4855950</v>
+      </c>
+      <c r="K59">
+        <v>22888956</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>17736022</v>
+      </c>
+      <c r="C60">
+        <v>5607201</v>
+      </c>
+      <c r="D60">
+        <v>23343223</v>
+      </c>
+      <c r="E60">
+        <v>18520978</v>
+      </c>
+      <c r="F60">
+        <v>10912659</v>
+      </c>
+      <c r="G60">
+        <v>2596099</v>
+      </c>
+      <c r="H60">
+        <v>4752801</v>
+      </c>
+      <c r="I60">
+        <v>259419</v>
+      </c>
+      <c r="J60">
+        <v>4822245</v>
+      </c>
+      <c r="K60">
+        <v>23343223</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>17779201</v>
+      </c>
+      <c r="C61">
+        <v>5601486</v>
+      </c>
+      <c r="D61">
+        <v>23380687</v>
+      </c>
+      <c r="E61">
+        <v>18394667</v>
+      </c>
+      <c r="F61">
+        <v>10949818</v>
+      </c>
+      <c r="G61">
+        <v>2685183</v>
+      </c>
+      <c r="H61">
+        <v>4792365</v>
+      </c>
+      <c r="I61">
+        <v>-32699</v>
+      </c>
+      <c r="J61">
+        <v>4986020</v>
+      </c>
+      <c r="K61">
+        <v>23380687</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>17816050</v>
+      </c>
+      <c r="C62">
+        <v>5503229</v>
+      </c>
+      <c r="D62">
+        <v>23319279</v>
+      </c>
+      <c r="E62">
+        <v>18357797</v>
+      </c>
+      <c r="F62">
+        <v>10991124</v>
+      </c>
+      <c r="G62">
+        <v>2650692</v>
+      </c>
+      <c r="H62">
+        <v>4662570</v>
+      </c>
+      <c r="I62">
+        <v>53411</v>
+      </c>
+      <c r="J62">
+        <v>4961482</v>
+      </c>
+      <c r="K62">
+        <v>23319279</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>17537769</v>
+      </c>
+      <c r="C63">
+        <v>5067061</v>
+      </c>
+      <c r="D63">
+        <v>22604830</v>
+      </c>
+      <c r="E63">
+        <v>17836913</v>
+      </c>
+      <c r="F63">
+        <v>10800258</v>
+      </c>
+      <c r="G63">
+        <v>2630538</v>
+      </c>
+      <c r="H63">
+        <v>4385434</v>
+      </c>
+      <c r="I63">
+        <v>20683</v>
+      </c>
+      <c r="J63">
+        <v>4767917</v>
+      </c>
+      <c r="K63">
+        <v>22604830</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>17492225</v>
+      </c>
+      <c r="C64">
+        <v>4774845</v>
+      </c>
+      <c r="D64">
+        <v>22267070</v>
+      </c>
+      <c r="E64">
+        <v>17482485</v>
+      </c>
+      <c r="F64">
+        <v>10700896</v>
+      </c>
+      <c r="G64">
+        <v>2634207</v>
+      </c>
+      <c r="H64">
+        <v>4240543</v>
+      </c>
+      <c r="I64">
+        <v>-93161</v>
+      </c>
+      <c r="J64">
+        <v>4784585</v>
+      </c>
+      <c r="K64">
+        <v>22267070</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>17328633</v>
+      </c>
+      <c r="C65">
+        <v>4562216</v>
+      </c>
+      <c r="D65">
+        <v>21890849</v>
+      </c>
+      <c r="E65">
+        <v>17186065</v>
+      </c>
+      <c r="F65">
+        <v>10556968</v>
+      </c>
+      <c r="G65">
+        <v>2556360</v>
+      </c>
+      <c r="H65">
+        <v>4176733</v>
+      </c>
+      <c r="I65">
+        <v>-103996</v>
+      </c>
+      <c r="J65">
+        <v>4704784</v>
+      </c>
+      <c r="K65">
+        <v>21890849</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>17204627</v>
+      </c>
+      <c r="C66">
+        <v>4446370</v>
+      </c>
+      <c r="D66">
+        <v>21650997</v>
+      </c>
+      <c r="E66">
+        <v>16862051</v>
+      </c>
+      <c r="F66">
+        <v>10435372</v>
+      </c>
+      <c r="G66">
+        <v>2612658</v>
+      </c>
+      <c r="H66">
+        <v>4050859</v>
+      </c>
+      <c r="I66">
+        <v>-236838</v>
+      </c>
+      <c r="J66">
+        <v>4788946</v>
+      </c>
+      <c r="K66">
+        <v>21650997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>17328097</v>
+      </c>
+      <c r="C67">
+        <v>4368593</v>
+      </c>
+      <c r="D67">
+        <v>21696690</v>
+      </c>
+      <c r="E67">
+        <v>16798696</v>
+      </c>
+      <c r="F67">
+        <v>10424941</v>
+      </c>
+      <c r="G67">
+        <v>2628205</v>
+      </c>
+      <c r="H67">
+        <v>3960281</v>
+      </c>
+      <c r="I67">
+        <v>-214731</v>
+      </c>
+      <c r="J67">
+        <v>4897994</v>
+      </c>
+      <c r="K67">
+        <v>21696690</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>17310908</v>
+      </c>
+      <c r="C68">
+        <v>4487944</v>
+      </c>
+      <c r="D68">
+        <v>21798852</v>
+      </c>
+      <c r="E68">
+        <v>16875789</v>
+      </c>
+      <c r="F68">
+        <v>10542320</v>
+      </c>
+      <c r="G68">
+        <v>2598395</v>
+      </c>
+      <c r="H68">
+        <v>3953201</v>
+      </c>
+      <c r="I68">
+        <v>-218127</v>
+      </c>
+      <c r="J68">
+        <v>4923063</v>
+      </c>
+      <c r="K68">
+        <v>21798852</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>17470434</v>
+      </c>
+      <c r="C69">
+        <v>4689290</v>
+      </c>
+      <c r="D69">
+        <v>22159724</v>
+      </c>
+      <c r="E69">
+        <v>17277845</v>
+      </c>
+      <c r="F69">
+        <v>10608933</v>
+      </c>
+      <c r="G69">
+        <v>2614639</v>
+      </c>
+      <c r="H69">
+        <v>3952763</v>
+      </c>
+      <c r="I69">
+        <v>101510</v>
+      </c>
+      <c r="J69">
+        <v>4881879</v>
+      </c>
+      <c r="K69">
+        <v>22159724</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>17497935</v>
+      </c>
+      <c r="C70">
+        <v>4847348</v>
+      </c>
+      <c r="D70">
+        <v>22345283</v>
+      </c>
+      <c r="E70">
+        <v>17471891</v>
+      </c>
+      <c r="F70">
+        <v>10759891</v>
+      </c>
+      <c r="G70">
+        <v>2670662</v>
+      </c>
+      <c r="H70">
+        <v>4104274</v>
+      </c>
+      <c r="I70">
+        <v>-62936</v>
+      </c>
+      <c r="J70">
+        <v>4873392</v>
+      </c>
+      <c r="K70">
+        <v>22345283</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>17685968</v>
+      </c>
+      <c r="C71">
+        <v>4982000</v>
+      </c>
+      <c r="D71">
+        <v>22667968</v>
+      </c>
+      <c r="E71">
+        <v>17750534</v>
+      </c>
+      <c r="F71">
+        <v>10816040</v>
+      </c>
+      <c r="G71">
+        <v>2672139</v>
+      </c>
+      <c r="H71">
+        <v>4171809</v>
+      </c>
+      <c r="I71">
+        <v>90546</v>
+      </c>
+      <c r="J71">
+        <v>4917434</v>
+      </c>
+      <c r="K71">
+        <v>22667968</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>17819405</v>
+      </c>
+      <c r="C72">
+        <v>5121848</v>
+      </c>
+      <c r="D72">
+        <v>22941253</v>
+      </c>
+      <c r="E72">
+        <v>17999660</v>
+      </c>
+      <c r="F72">
+        <v>10922922</v>
+      </c>
+      <c r="G72">
+        <v>2713251</v>
+      </c>
+      <c r="H72">
+        <v>4230772</v>
+      </c>
+      <c r="I72">
+        <v>132715</v>
+      </c>
+      <c r="J72">
+        <v>4941593</v>
+      </c>
+      <c r="K72">
+        <v>22941253</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>17952383</v>
+      </c>
+      <c r="C73">
+        <v>5242600</v>
+      </c>
+      <c r="D73">
+        <v>23194983</v>
+      </c>
+      <c r="E73">
+        <v>18295755</v>
+      </c>
+      <c r="F73">
+        <v>11078702</v>
+      </c>
+      <c r="G73">
+        <v>2733955</v>
+      </c>
+      <c r="H73">
+        <v>4255444</v>
+      </c>
+      <c r="I73">
+        <v>227654</v>
+      </c>
+      <c r="J73">
+        <v>4899228</v>
+      </c>
+      <c r="K73">
+        <v>23194983</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74">
+        <v>17762564</v>
+      </c>
+      <c r="C74">
+        <v>5280576</v>
+      </c>
+      <c r="D74">
+        <v>23043140</v>
+      </c>
+      <c r="E74">
+        <v>18066160</v>
+      </c>
+      <c r="F74">
+        <v>10943529</v>
+      </c>
+      <c r="G74">
+        <v>2733137</v>
+      </c>
+      <c r="H74">
+        <v>4274960</v>
+      </c>
+      <c r="I74">
+        <v>114534</v>
+      </c>
+      <c r="J74">
+        <v>4976980</v>
+      </c>
+      <c r="K74">
+        <v>23043140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75">
+        <v>17943194</v>
+      </c>
+      <c r="C75">
+        <v>5188314</v>
+      </c>
+      <c r="D75">
+        <v>23131508</v>
+      </c>
+      <c r="E75">
+        <v>18198478</v>
+      </c>
+      <c r="F75">
+        <v>11046394</v>
+      </c>
+      <c r="G75">
+        <v>2795010</v>
+      </c>
+      <c r="H75">
+        <v>4292930</v>
+      </c>
+      <c r="I75">
+        <v>64144</v>
+      </c>
+      <c r="J75">
+        <v>4933030</v>
+      </c>
+      <c r="K75">
+        <v>23131508</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76">
+        <v>18080826</v>
+      </c>
+      <c r="C76">
+        <v>5307135</v>
+      </c>
+      <c r="D76">
+        <v>23387961</v>
+      </c>
+      <c r="E76">
+        <v>18425574</v>
+      </c>
+      <c r="F76">
+        <v>11189794</v>
+      </c>
+      <c r="G76">
+        <v>2794099</v>
+      </c>
+      <c r="H76">
+        <v>4313990</v>
+      </c>
+      <c r="I76">
+        <v>127691</v>
+      </c>
+      <c r="J76">
+        <v>4962387</v>
+      </c>
+      <c r="K76">
+        <v>23387961</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77">
+        <v>18083933</v>
+      </c>
+      <c r="C77">
+        <v>5307144</v>
+      </c>
+      <c r="D77">
+        <v>23391077</v>
+      </c>
+      <c r="E77">
+        <v>18405265</v>
+      </c>
+      <c r="F77">
+        <v>11307325</v>
+      </c>
+      <c r="G77">
+        <v>2844942</v>
+      </c>
+      <c r="H77">
+        <v>4211127</v>
+      </c>
+      <c r="I77">
+        <v>41871</v>
+      </c>
+      <c r="J77">
+        <v>4985812</v>
+      </c>
+      <c r="K77">
+        <v>23391077</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78">
+        <v>17970651</v>
+      </c>
+      <c r="C78">
+        <v>5354583</v>
+      </c>
+      <c r="D78">
+        <v>23325234</v>
+      </c>
+      <c r="E78">
+        <v>18338888</v>
+      </c>
+      <c r="F78">
+        <v>11153387</v>
+      </c>
+      <c r="G78">
+        <v>2740228</v>
+      </c>
+      <c r="H78">
+        <v>4128725</v>
+      </c>
+      <c r="I78">
+        <v>316548</v>
+      </c>
+      <c r="J78">
+        <v>4986346</v>
+      </c>
+      <c r="K78">
+        <v>23325234</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79">
+        <v>18009165</v>
+      </c>
+      <c r="C79">
+        <v>5367090</v>
+      </c>
+      <c r="D79">
+        <v>23376255</v>
+      </c>
+      <c r="E79">
+        <v>18168033</v>
+      </c>
+      <c r="F79">
+        <v>11148536</v>
+      </c>
+      <c r="G79">
+        <v>2760664</v>
+      </c>
+      <c r="H79">
+        <v>4085013</v>
+      </c>
+      <c r="I79">
+        <v>173820</v>
+      </c>
+      <c r="J79">
+        <v>5208222</v>
+      </c>
+      <c r="K79">
+        <v>23376255</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80">
+        <v>18075353</v>
+      </c>
+      <c r="C80">
+        <v>5336578</v>
+      </c>
+      <c r="D80">
+        <v>23411931</v>
+      </c>
+      <c r="E80">
+        <v>18182999</v>
+      </c>
+      <c r="F80">
+        <v>11180116</v>
+      </c>
+      <c r="G80">
+        <v>2720778</v>
+      </c>
+      <c r="H80">
+        <v>4195374</v>
+      </c>
+      <c r="I80">
+        <v>86731</v>
+      </c>
+      <c r="J80">
+        <v>5228932</v>
+      </c>
+      <c r="K80">
+        <v>23411931</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81">
+        <v>17824048</v>
+      </c>
+      <c r="C81">
+        <v>5093114</v>
+      </c>
+      <c r="D81">
+        <v>22917162</v>
+      </c>
+      <c r="E81">
+        <v>17758497</v>
+      </c>
+      <c r="F81">
+        <v>11133554</v>
+      </c>
+      <c r="G81">
+        <v>2723654</v>
+      </c>
+      <c r="H81">
+        <v>4119638</v>
+      </c>
+      <c r="I81">
+        <v>-218349</v>
+      </c>
+      <c r="J81">
+        <v>5158665</v>
+      </c>
+      <c r="K81">
+        <v>22917162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82">
+        <v>17627306</v>
+      </c>
+      <c r="C82">
+        <v>5388324</v>
+      </c>
+      <c r="D82">
+        <v>23015630</v>
+      </c>
+      <c r="E82">
+        <v>17837182</v>
+      </c>
+      <c r="F82">
+        <v>11083764</v>
+      </c>
+      <c r="G82">
+        <v>2704678</v>
+      </c>
+      <c r="H82">
+        <v>3996485</v>
+      </c>
+      <c r="I82">
+        <v>52255</v>
+      </c>
+      <c r="J82">
+        <v>5178448</v>
+      </c>
+      <c r="K82">
+        <v>23015630</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83">
+        <v>15709655</v>
+      </c>
+      <c r="C83">
+        <v>4319103</v>
+      </c>
+      <c r="D83">
+        <v>20028758</v>
+      </c>
+      <c r="E83">
+        <v>15609074</v>
+      </c>
+      <c r="F83">
+        <v>9847019</v>
+      </c>
+      <c r="G83">
+        <v>2514435</v>
+      </c>
+      <c r="H83">
+        <v>3359140</v>
+      </c>
+      <c r="I83">
+        <v>-111520</v>
+      </c>
+      <c r="J83">
+        <v>4419684</v>
+      </c>
+      <c r="K83">
+        <v>20028758</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84">
+        <v>16439169</v>
+      </c>
+      <c r="C84">
+        <v>4698902</v>
+      </c>
+      <c r="D84">
+        <v>21138071</v>
+      </c>
+      <c r="E84">
+        <v>15900633</v>
+      </c>
+      <c r="F84">
+        <v>10182225</v>
+      </c>
+      <c r="G84">
+        <v>2516966</v>
+      </c>
+      <c r="H84">
+        <v>3559745</v>
+      </c>
+      <c r="I84">
+        <v>-358303</v>
+      </c>
+      <c r="J84">
+        <v>5237438</v>
+      </c>
+      <c r="K84">
+        <v>21138071</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85">
+        <v>16532359</v>
+      </c>
+      <c r="C85">
+        <v>5077732</v>
+      </c>
+      <c r="D85">
+        <v>21610091</v>
+      </c>
+      <c r="E85">
+        <v>16301248</v>
+      </c>
+      <c r="F85">
+        <v>10385181</v>
+      </c>
+      <c r="G85">
+        <v>2538849</v>
+      </c>
+      <c r="H85">
+        <v>3643982</v>
+      </c>
+      <c r="I85">
+        <v>-266764</v>
+      </c>
+      <c r="J85">
+        <v>5308843</v>
+      </c>
+      <c r="K85">
+        <v>21610091</v>
       </c>
     </row>
   </sheetData>
